--- a/data/macro/South Korea/South Korea Export.xlsx
+++ b/data/macro/South Korea/South Korea Export.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\South Korea\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B21814-D3F6-42E2-8222-76E643C92FD0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AA0A8C-4EA8-4BA2-917D-97CF634EACF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11580" xr2:uid="{D0939876-3207-4808-9706-D07754E61412}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0939876-3207-4808-9706-D07754E61412}"/>
   </bookViews>
   <sheets>
     <sheet name="KR Export" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="13">
   <si>
     <t>Release Date</t>
   </si>
@@ -55,9 +55,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://kr.investing.com/economic-calendar/south-korean-export-growth-1316</t>
-  </si>
-  <si>
     <t>frequency</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -73,6 +70,10 @@
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>https://kr.investing.com/economic-calendar/south-korean-export-growth-1316</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -84,9 +85,9 @@
     <numFmt numFmtId="178" formatCode="[$-409]h:mm\ AM/PM;@"/>
     <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="180" formatCode="0.0%"/>
-    <numFmt numFmtId="182" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -128,6 +129,14 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -146,7 +155,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -156,8 +165,11 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -197,17 +209,21 @@
     <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="3" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -519,24 +535,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E811BE6-6834-4321-8CFC-3896E109A5F4}">
-  <dimension ref="A1:J786"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J788"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="5"/>
+    <col min="8" max="8" width="26.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -557,10 +573,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>25538</v>
       </c>
@@ -579,7 +595,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="10"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>25569</v>
       </c>
@@ -600,7 +616,7 @@
       </c>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>25600</v>
       </c>
@@ -621,7 +637,7 @@
       </c>
       <c r="I4" s="9"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>25628</v>
       </c>
@@ -642,7 +658,7 @@
       </c>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>25659</v>
       </c>
@@ -663,7 +679,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>25689</v>
       </c>
@@ -684,7 +700,7 @@
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>25720</v>
       </c>
@@ -705,7 +721,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>25750</v>
       </c>
@@ -726,7 +742,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>25781</v>
       </c>
@@ -747,7 +763,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>25812</v>
       </c>
@@ -768,7 +784,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>25842</v>
       </c>
@@ -789,7 +805,7 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>25873</v>
       </c>
@@ -810,7 +826,7 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>25903</v>
       </c>
@@ -831,7 +847,7 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>25934</v>
       </c>
@@ -852,7 +868,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>25965</v>
       </c>
@@ -873,7 +889,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>25993</v>
       </c>
@@ -894,7 +910,7 @@
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>26024</v>
       </c>
@@ -915,7 +931,7 @@
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>26054</v>
       </c>
@@ -936,7 +952,7 @@
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>26085</v>
       </c>
@@ -957,7 +973,7 @@
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>26115</v>
       </c>
@@ -978,7 +994,7 @@
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>26146</v>
       </c>
@@ -999,7 +1015,7 @@
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>26177</v>
       </c>
@@ -1020,7 +1036,7 @@
       </c>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>26207</v>
       </c>
@@ -1041,7 +1057,7 @@
       </c>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>26238</v>
       </c>
@@ -1062,7 +1078,7 @@
       </c>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>26268</v>
       </c>
@@ -1083,7 +1099,7 @@
       </c>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>26299</v>
       </c>
@@ -1104,7 +1120,7 @@
       </c>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>26330</v>
       </c>
@@ -1125,7 +1141,7 @@
       </c>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>26359</v>
       </c>
@@ -1146,7 +1162,7 @@
       </c>
       <c r="I29" s="9"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>26390</v>
       </c>
@@ -1167,7 +1183,7 @@
       </c>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>26420</v>
       </c>
@@ -1188,7 +1204,7 @@
       </c>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>26451</v>
       </c>
@@ -1209,7 +1225,7 @@
       </c>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>26481</v>
       </c>
@@ -1230,7 +1246,7 @@
       </c>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>26512</v>
       </c>
@@ -1251,7 +1267,7 @@
       </c>
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>26543</v>
       </c>
@@ -1272,7 +1288,7 @@
       </c>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>26573</v>
       </c>
@@ -1293,7 +1309,7 @@
       </c>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>26604</v>
       </c>
@@ -1314,7 +1330,7 @@
       </c>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>26634</v>
       </c>
@@ -1335,7 +1351,7 @@
       </c>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>26665</v>
       </c>
@@ -1356,7 +1372,7 @@
       </c>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>26696</v>
       </c>
@@ -1377,7 +1393,7 @@
       </c>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>26724</v>
       </c>
@@ -1398,7 +1414,7 @@
       </c>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>26755</v>
       </c>
@@ -1419,7 +1435,7 @@
       </c>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>26785</v>
       </c>
@@ -1440,7 +1456,7 @@
       </c>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>26816</v>
       </c>
@@ -1461,7 +1477,7 @@
       </c>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>26846</v>
       </c>
@@ -1482,7 +1498,7 @@
       </c>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>26877</v>
       </c>
@@ -1503,7 +1519,7 @@
       </c>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>26908</v>
       </c>
@@ -1524,7 +1540,7 @@
       </c>
       <c r="I47" s="9"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>26938</v>
       </c>
@@ -1545,7 +1561,7 @@
       </c>
       <c r="I48" s="9"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>26969</v>
       </c>
@@ -1566,7 +1582,7 @@
       </c>
       <c r="I49" s="9"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>26999</v>
       </c>
@@ -1587,7 +1603,7 @@
       </c>
       <c r="I50" s="9"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>27030</v>
       </c>
@@ -1608,7 +1624,7 @@
       </c>
       <c r="I51" s="9"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>27061</v>
       </c>
@@ -1629,7 +1645,7 @@
       </c>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>27089</v>
       </c>
@@ -1650,7 +1666,7 @@
       </c>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>27120</v>
       </c>
@@ -1671,7 +1687,7 @@
       </c>
       <c r="I54" s="9"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>27150</v>
       </c>
@@ -1692,7 +1708,7 @@
       </c>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>27181</v>
       </c>
@@ -1713,7 +1729,7 @@
       </c>
       <c r="I56" s="9"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>27211</v>
       </c>
@@ -1734,7 +1750,7 @@
       </c>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>27242</v>
       </c>
@@ -1755,7 +1771,7 @@
       </c>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>27273</v>
       </c>
@@ -1776,7 +1792,7 @@
       </c>
       <c r="I59" s="9"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>27303</v>
       </c>
@@ -1797,7 +1813,7 @@
       </c>
       <c r="I60" s="9"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>27334</v>
       </c>
@@ -1818,7 +1834,7 @@
       </c>
       <c r="I61" s="9"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>27364</v>
       </c>
@@ -1839,7 +1855,7 @@
       </c>
       <c r="I62" s="9"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>27395</v>
       </c>
@@ -1860,7 +1876,7 @@
       </c>
       <c r="I63" s="9"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>27426</v>
       </c>
@@ -1881,7 +1897,7 @@
       </c>
       <c r="I64" s="9"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>27454</v>
       </c>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>27485</v>
       </c>
@@ -1923,7 +1939,7 @@
       </c>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>27515</v>
       </c>
@@ -1944,7 +1960,7 @@
       </c>
       <c r="I67" s="9"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>27546</v>
       </c>
@@ -1965,7 +1981,7 @@
       </c>
       <c r="I68" s="9"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>27576</v>
       </c>
@@ -1986,7 +2002,7 @@
       </c>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>27607</v>
       </c>
@@ -2007,7 +2023,7 @@
       </c>
       <c r="I70" s="9"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>27638</v>
       </c>
@@ -2028,7 +2044,7 @@
       </c>
       <c r="I71" s="9"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>27668</v>
       </c>
@@ -2049,7 +2065,7 @@
       </c>
       <c r="I72" s="9"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>27699</v>
       </c>
@@ -2070,7 +2086,7 @@
       </c>
       <c r="I73" s="9"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="6">
         <v>27729</v>
       </c>
@@ -2091,7 +2107,7 @@
       </c>
       <c r="I74" s="9"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>27760</v>
       </c>
@@ -2112,7 +2128,7 @@
       </c>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>27791</v>
       </c>
@@ -2133,7 +2149,7 @@
       </c>
       <c r="I76" s="9"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>27820</v>
       </c>
@@ -2154,7 +2170,7 @@
       </c>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>27851</v>
       </c>
@@ -2175,7 +2191,7 @@
       </c>
       <c r="I78" s="9"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>27881</v>
       </c>
@@ -2196,7 +2212,7 @@
       </c>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>27912</v>
       </c>
@@ -2217,7 +2233,7 @@
       </c>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>27942</v>
       </c>
@@ -2238,7 +2254,7 @@
       </c>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>27973</v>
       </c>
@@ -2259,7 +2275,7 @@
       </c>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>28004</v>
       </c>
@@ -2280,7 +2296,7 @@
       </c>
       <c r="I83" s="9"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>28034</v>
       </c>
@@ -2301,7 +2317,7 @@
       </c>
       <c r="I84" s="9"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>28065</v>
       </c>
@@ -2322,7 +2338,7 @@
       </c>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>28095</v>
       </c>
@@ -2343,7 +2359,7 @@
       </c>
       <c r="I86" s="9"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>28126</v>
       </c>
@@ -2364,7 +2380,7 @@
       </c>
       <c r="I87" s="9"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>28157</v>
       </c>
@@ -2385,7 +2401,7 @@
       </c>
       <c r="I88" s="9"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="6">
         <v>28185</v>
       </c>
@@ -2406,7 +2422,7 @@
       </c>
       <c r="I89" s="9"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="6">
         <v>28216</v>
       </c>
@@ -2427,7 +2443,7 @@
       </c>
       <c r="I90" s="9"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="6">
         <v>28246</v>
       </c>
@@ -2448,7 +2464,7 @@
       </c>
       <c r="I91" s="9"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="6">
         <v>28277</v>
       </c>
@@ -2469,7 +2485,7 @@
       </c>
       <c r="I92" s="9"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="6">
         <v>28307</v>
       </c>
@@ -2490,7 +2506,7 @@
       </c>
       <c r="I93" s="9"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="6">
         <v>28338</v>
       </c>
@@ -2511,7 +2527,7 @@
       </c>
       <c r="I94" s="9"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="6">
         <v>28369</v>
       </c>
@@ -2532,7 +2548,7 @@
       </c>
       <c r="I95" s="9"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="6">
         <v>28399</v>
       </c>
@@ -2553,7 +2569,7 @@
       </c>
       <c r="I96" s="9"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="6">
         <v>28430</v>
       </c>
@@ -2574,7 +2590,7 @@
       </c>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="6">
         <v>28460</v>
       </c>
@@ -2595,7 +2611,7 @@
       </c>
       <c r="I98" s="9"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="6">
         <v>28491</v>
       </c>
@@ -2616,7 +2632,7 @@
       </c>
       <c r="I99" s="9"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="6">
         <v>28522</v>
       </c>
@@ -2637,7 +2653,7 @@
       </c>
       <c r="I100" s="9"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="6">
         <v>28550</v>
       </c>
@@ -2658,7 +2674,7 @@
       </c>
       <c r="I101" s="9"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="6">
         <v>28581</v>
       </c>
@@ -2679,7 +2695,7 @@
       </c>
       <c r="I102" s="9"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="6">
         <v>28611</v>
       </c>
@@ -2700,7 +2716,7 @@
       </c>
       <c r="I103" s="9"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="6">
         <v>28642</v>
       </c>
@@ -2721,7 +2737,7 @@
       </c>
       <c r="I104" s="9"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="6">
         <v>28672</v>
       </c>
@@ -2742,7 +2758,7 @@
       </c>
       <c r="I105" s="9"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="6">
         <v>28703</v>
       </c>
@@ -2763,7 +2779,7 @@
       </c>
       <c r="I106" s="9"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="6">
         <v>28734</v>
       </c>
@@ -2784,7 +2800,7 @@
       </c>
       <c r="I107" s="9"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="6">
         <v>28764</v>
       </c>
@@ -2805,7 +2821,7 @@
       </c>
       <c r="I108" s="9"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="6">
         <v>28795</v>
       </c>
@@ -2826,7 +2842,7 @@
       </c>
       <c r="I109" s="9"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="6">
         <v>28825</v>
       </c>
@@ -2847,7 +2863,7 @@
       </c>
       <c r="I110" s="9"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="6">
         <v>28856</v>
       </c>
@@ -2868,7 +2884,7 @@
       </c>
       <c r="I111" s="9"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="6">
         <v>28887</v>
       </c>
@@ -2889,7 +2905,7 @@
       </c>
       <c r="I112" s="9"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="6">
         <v>28915</v>
       </c>
@@ -2910,7 +2926,7 @@
       </c>
       <c r="I113" s="9"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="6">
         <v>28946</v>
       </c>
@@ -2931,7 +2947,7 @@
       </c>
       <c r="I114" s="9"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="6">
         <v>28976</v>
       </c>
@@ -2952,7 +2968,7 @@
       </c>
       <c r="I115" s="9"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="6">
         <v>29007</v>
       </c>
@@ -2973,7 +2989,7 @@
       </c>
       <c r="I116" s="9"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="6">
         <v>29037</v>
       </c>
@@ -2994,7 +3010,7 @@
       </c>
       <c r="I117" s="9"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="6">
         <v>29068</v>
       </c>
@@ -3015,7 +3031,7 @@
       </c>
       <c r="I118" s="9"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="6">
         <v>29099</v>
       </c>
@@ -3036,7 +3052,7 @@
       </c>
       <c r="I119" s="9"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="6">
         <v>29129</v>
       </c>
@@ -3057,7 +3073,7 @@
       </c>
       <c r="I120" s="9"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="6">
         <v>29160</v>
       </c>
@@ -3078,7 +3094,7 @@
       </c>
       <c r="I121" s="9"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="6">
         <v>29190</v>
       </c>
@@ -3099,7 +3115,7 @@
       </c>
       <c r="I122" s="9"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="6">
         <v>29221</v>
       </c>
@@ -3120,7 +3136,7 @@
       </c>
       <c r="I123" s="9"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="6">
         <v>29252</v>
       </c>
@@ -3141,7 +3157,7 @@
       </c>
       <c r="I124" s="9"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="6">
         <v>29281</v>
       </c>
@@ -3162,7 +3178,7 @@
       </c>
       <c r="I125" s="9"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="6">
         <v>29312</v>
       </c>
@@ -3183,7 +3199,7 @@
       </c>
       <c r="I126" s="9"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="6">
         <v>29342</v>
       </c>
@@ -3204,7 +3220,7 @@
       </c>
       <c r="I127" s="9"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="6">
         <v>29373</v>
       </c>
@@ -3225,7 +3241,7 @@
       </c>
       <c r="I128" s="9"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="6">
         <v>29403</v>
       </c>
@@ -3246,7 +3262,7 @@
       </c>
       <c r="I129" s="9"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="6">
         <v>29434</v>
       </c>
@@ -3267,7 +3283,7 @@
       </c>
       <c r="I130" s="9"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="6">
         <v>29465</v>
       </c>
@@ -3288,7 +3304,7 @@
       </c>
       <c r="I131" s="9"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="6">
         <v>29495</v>
       </c>
@@ -3309,7 +3325,7 @@
       </c>
       <c r="I132" s="9"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="6">
         <v>29526</v>
       </c>
@@ -3330,7 +3346,7 @@
       </c>
       <c r="I133" s="9"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="6">
         <v>29556</v>
       </c>
@@ -3351,7 +3367,7 @@
       </c>
       <c r="I134" s="9"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="6">
         <v>29587</v>
       </c>
@@ -3372,7 +3388,7 @@
       </c>
       <c r="I135" s="9"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="6">
         <v>29618</v>
       </c>
@@ -3393,7 +3409,7 @@
       </c>
       <c r="I136" s="9"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="6">
         <v>29646</v>
       </c>
@@ -3414,7 +3430,7 @@
       </c>
       <c r="I137" s="9"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="6">
         <v>29677</v>
       </c>
@@ -3435,7 +3451,7 @@
       </c>
       <c r="I138" s="9"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="6">
         <v>29707</v>
       </c>
@@ -3456,7 +3472,7 @@
       </c>
       <c r="I139" s="9"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="6">
         <v>29738</v>
       </c>
@@ -3477,7 +3493,7 @@
       </c>
       <c r="I140" s="9"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="6">
         <v>29768</v>
       </c>
@@ -3498,7 +3514,7 @@
       </c>
       <c r="I141" s="9"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="6">
         <v>29799</v>
       </c>
@@ -3519,7 +3535,7 @@
       </c>
       <c r="I142" s="9"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="6">
         <v>29830</v>
       </c>
@@ -3540,7 +3556,7 @@
       </c>
       <c r="I143" s="9"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="6">
         <v>29860</v>
       </c>
@@ -3561,7 +3577,7 @@
       </c>
       <c r="I144" s="9"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="6">
         <v>29891</v>
       </c>
@@ -3582,7 +3598,7 @@
       </c>
       <c r="I145" s="9"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="6">
         <v>29921</v>
       </c>
@@ -3603,7 +3619,7 @@
       </c>
       <c r="I146" s="9"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="6">
         <v>29952</v>
       </c>
@@ -3624,7 +3640,7 @@
       </c>
       <c r="I147" s="9"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="6">
         <v>29983</v>
       </c>
@@ -3645,7 +3661,7 @@
       </c>
       <c r="I148" s="9"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="6">
         <v>30011</v>
       </c>
@@ -3666,7 +3682,7 @@
       </c>
       <c r="I149" s="9"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="6">
         <v>30042</v>
       </c>
@@ -3687,7 +3703,7 @@
       </c>
       <c r="I150" s="9"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="6">
         <v>30072</v>
       </c>
@@ -3708,7 +3724,7 @@
       </c>
       <c r="I151" s="9"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="6">
         <v>30103</v>
       </c>
@@ -3729,7 +3745,7 @@
       </c>
       <c r="I152" s="9"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="6">
         <v>30133</v>
       </c>
@@ -3750,7 +3766,7 @@
       </c>
       <c r="I153" s="9"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="6">
         <v>30164</v>
       </c>
@@ -3771,7 +3787,7 @@
       </c>
       <c r="I154" s="9"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="6">
         <v>30195</v>
       </c>
@@ -3792,7 +3808,7 @@
       </c>
       <c r="I155" s="9"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="6">
         <v>30225</v>
       </c>
@@ -3813,7 +3829,7 @@
       </c>
       <c r="I156" s="9"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="6">
         <v>30256</v>
       </c>
@@ -3834,7 +3850,7 @@
       </c>
       <c r="I157" s="9"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="6">
         <v>30286</v>
       </c>
@@ -3855,7 +3871,7 @@
       </c>
       <c r="I158" s="9"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="6">
         <v>30317</v>
       </c>
@@ -3876,7 +3892,7 @@
       </c>
       <c r="I159" s="9"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="6">
         <v>30348</v>
       </c>
@@ -3897,7 +3913,7 @@
       </c>
       <c r="I160" s="9"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="6">
         <v>30376</v>
       </c>
@@ -3918,7 +3934,7 @@
       </c>
       <c r="I161" s="9"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="6">
         <v>30407</v>
       </c>
@@ -3939,7 +3955,7 @@
       </c>
       <c r="I162" s="9"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="6">
         <v>30437</v>
       </c>
@@ -3960,7 +3976,7 @@
       </c>
       <c r="I163" s="9"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="6">
         <v>30468</v>
       </c>
@@ -3981,7 +3997,7 @@
       </c>
       <c r="I164" s="9"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="6">
         <v>30498</v>
       </c>
@@ -4002,7 +4018,7 @@
       </c>
       <c r="I165" s="9"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="6">
         <v>30529</v>
       </c>
@@ -4023,7 +4039,7 @@
       </c>
       <c r="I166" s="9"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="6">
         <v>30560</v>
       </c>
@@ -4044,7 +4060,7 @@
       </c>
       <c r="I167" s="9"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="6">
         <v>30590</v>
       </c>
@@ -4065,7 +4081,7 @@
       </c>
       <c r="I168" s="9"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="6">
         <v>30621</v>
       </c>
@@ -4086,7 +4102,7 @@
       </c>
       <c r="I169" s="9"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="6">
         <v>30651</v>
       </c>
@@ -4107,7 +4123,7 @@
       </c>
       <c r="I170" s="9"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="6">
         <v>30682</v>
       </c>
@@ -4128,7 +4144,7 @@
       </c>
       <c r="I171" s="9"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="6">
         <v>30713</v>
       </c>
@@ -4149,7 +4165,7 @@
       </c>
       <c r="I172" s="9"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="6">
         <v>30742</v>
       </c>
@@ -4170,7 +4186,7 @@
       </c>
       <c r="I173" s="9"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="6">
         <v>30773</v>
       </c>
@@ -4191,7 +4207,7 @@
       </c>
       <c r="I174" s="9"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="6">
         <v>30803</v>
       </c>
@@ -4212,7 +4228,7 @@
       </c>
       <c r="I175" s="9"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="6">
         <v>30834</v>
       </c>
@@ -4233,7 +4249,7 @@
       </c>
       <c r="I176" s="9"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="6">
         <v>30864</v>
       </c>
@@ -4254,7 +4270,7 @@
       </c>
       <c r="I177" s="9"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="6">
         <v>30895</v>
       </c>
@@ -4275,7 +4291,7 @@
       </c>
       <c r="I178" s="9"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="6">
         <v>30926</v>
       </c>
@@ -4296,7 +4312,7 @@
       </c>
       <c r="I179" s="9"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="6">
         <v>30956</v>
       </c>
@@ -4317,7 +4333,7 @@
       </c>
       <c r="I180" s="9"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="6">
         <v>30987</v>
       </c>
@@ -4338,7 +4354,7 @@
       </c>
       <c r="I181" s="9"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="6">
         <v>31017</v>
       </c>
@@ -4359,7 +4375,7 @@
       </c>
       <c r="I182" s="9"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="6">
         <v>31048</v>
       </c>
@@ -4380,7 +4396,7 @@
       </c>
       <c r="I183" s="9"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="6">
         <v>31079</v>
       </c>
@@ -4401,7 +4417,7 @@
       </c>
       <c r="I184" s="9"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="6">
         <v>31107</v>
       </c>
@@ -4422,7 +4438,7 @@
       </c>
       <c r="I185" s="9"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="6">
         <v>31138</v>
       </c>
@@ -4443,7 +4459,7 @@
       </c>
       <c r="I186" s="9"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="6">
         <v>31168</v>
       </c>
@@ -4464,7 +4480,7 @@
       </c>
       <c r="I187" s="9"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="6">
         <v>31199</v>
       </c>
@@ -4485,7 +4501,7 @@
       </c>
       <c r="I188" s="9"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="6">
         <v>31229</v>
       </c>
@@ -4506,7 +4522,7 @@
       </c>
       <c r="I189" s="9"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="6">
         <v>31260</v>
       </c>
@@ -4527,7 +4543,7 @@
       </c>
       <c r="I190" s="9"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="6">
         <v>31291</v>
       </c>
@@ -4548,7 +4564,7 @@
       </c>
       <c r="I191" s="9"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="6">
         <v>31321</v>
       </c>
@@ -4569,7 +4585,7 @@
       </c>
       <c r="I192" s="9"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="6">
         <v>31352</v>
       </c>
@@ -4590,7 +4606,7 @@
       </c>
       <c r="I193" s="9"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="6">
         <v>31382</v>
       </c>
@@ -4611,7 +4627,7 @@
       </c>
       <c r="I194" s="9"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="6">
         <v>31413</v>
       </c>
@@ -4632,7 +4648,7 @@
       </c>
       <c r="I195" s="9"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="6">
         <v>31444</v>
       </c>
@@ -4653,7 +4669,7 @@
       </c>
       <c r="I196" s="9"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="6">
         <v>31472</v>
       </c>
@@ -4674,7 +4690,7 @@
       </c>
       <c r="I197" s="9"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="6">
         <v>31503</v>
       </c>
@@ -4695,7 +4711,7 @@
       </c>
       <c r="I198" s="9"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="6">
         <v>31533</v>
       </c>
@@ -4716,7 +4732,7 @@
       </c>
       <c r="I199" s="9"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="6">
         <v>31564</v>
       </c>
@@ -4737,7 +4753,7 @@
       </c>
       <c r="I200" s="9"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="6">
         <v>31594</v>
       </c>
@@ -4758,7 +4774,7 @@
       </c>
       <c r="I201" s="9"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="6">
         <v>31625</v>
       </c>
@@ -4779,7 +4795,7 @@
       </c>
       <c r="I202" s="9"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="6">
         <v>31656</v>
       </c>
@@ -4800,7 +4816,7 @@
       </c>
       <c r="I203" s="9"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="6">
         <v>31686</v>
       </c>
@@ -4821,7 +4837,7 @@
       </c>
       <c r="I204" s="9"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="6">
         <v>31717</v>
       </c>
@@ -4842,7 +4858,7 @@
       </c>
       <c r="I205" s="9"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="6">
         <v>31747</v>
       </c>
@@ -4863,7 +4879,7 @@
       </c>
       <c r="I206" s="9"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="6">
         <v>31778</v>
       </c>
@@ -4884,7 +4900,7 @@
       </c>
       <c r="I207" s="9"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="6">
         <v>31809</v>
       </c>
@@ -4905,7 +4921,7 @@
       </c>
       <c r="I208" s="9"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="6">
         <v>31837</v>
       </c>
@@ -4926,7 +4942,7 @@
       </c>
       <c r="I209" s="9"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="6">
         <v>31868</v>
       </c>
@@ -4947,7 +4963,7 @@
       </c>
       <c r="I210" s="9"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="6">
         <v>31898</v>
       </c>
@@ -4968,7 +4984,7 @@
       </c>
       <c r="I211" s="9"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" s="6">
         <v>31929</v>
       </c>
@@ -4989,7 +5005,7 @@
       </c>
       <c r="I212" s="9"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="6">
         <v>31959</v>
       </c>
@@ -5010,7 +5026,7 @@
       </c>
       <c r="I213" s="9"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="6">
         <v>31990</v>
       </c>
@@ -5031,7 +5047,7 @@
       </c>
       <c r="I214" s="9"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="6">
         <v>32021</v>
       </c>
@@ -5052,7 +5068,7 @@
       </c>
       <c r="I215" s="9"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="6">
         <v>32051</v>
       </c>
@@ -5073,7 +5089,7 @@
       </c>
       <c r="I216" s="9"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="6">
         <v>32082</v>
       </c>
@@ -5094,7 +5110,7 @@
       </c>
       <c r="I217" s="9"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="6">
         <v>32112</v>
       </c>
@@ -5115,7 +5131,7 @@
       </c>
       <c r="I218" s="9"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="6">
         <v>32143</v>
       </c>
@@ -5136,7 +5152,7 @@
       </c>
       <c r="I219" s="9"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="6">
         <v>32174</v>
       </c>
@@ -5157,7 +5173,7 @@
       </c>
       <c r="I220" s="9"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" s="6">
         <v>32203</v>
       </c>
@@ -5178,7 +5194,7 @@
       </c>
       <c r="I221" s="9"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="6">
         <v>32234</v>
       </c>
@@ -5199,7 +5215,7 @@
       </c>
       <c r="I222" s="9"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="6">
         <v>32264</v>
       </c>
@@ -5220,7 +5236,7 @@
       </c>
       <c r="I223" s="9"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="6">
         <v>32295</v>
       </c>
@@ -5241,7 +5257,7 @@
       </c>
       <c r="I224" s="9"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="6">
         <v>32325</v>
       </c>
@@ -5262,7 +5278,7 @@
       </c>
       <c r="I225" s="9"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="6">
         <v>32356</v>
       </c>
@@ -5283,7 +5299,7 @@
       </c>
       <c r="I226" s="9"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" s="6">
         <v>32387</v>
       </c>
@@ -5304,7 +5320,7 @@
       </c>
       <c r="I227" s="9"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="6">
         <v>32417</v>
       </c>
@@ -5325,7 +5341,7 @@
       </c>
       <c r="I228" s="9"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="6">
         <v>32448</v>
       </c>
@@ -5346,7 +5362,7 @@
       </c>
       <c r="I229" s="9"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="6">
         <v>32478</v>
       </c>
@@ -5367,7 +5383,7 @@
       </c>
       <c r="I230" s="9"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="6">
         <v>32509</v>
       </c>
@@ -5388,7 +5404,7 @@
       </c>
       <c r="I231" s="9"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="6">
         <v>32540</v>
       </c>
@@ -5409,7 +5425,7 @@
       </c>
       <c r="I232" s="9"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="6">
         <v>32568</v>
       </c>
@@ -5430,7 +5446,7 @@
       </c>
       <c r="I233" s="9"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="6">
         <v>32599</v>
       </c>
@@ -5451,7 +5467,7 @@
       </c>
       <c r="I234" s="9"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="6">
         <v>32629</v>
       </c>
@@ -5472,7 +5488,7 @@
       </c>
       <c r="I235" s="9"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="6">
         <v>32660</v>
       </c>
@@ -5493,7 +5509,7 @@
       </c>
       <c r="I236" s="9"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" s="6">
         <v>32690</v>
       </c>
@@ -5514,7 +5530,7 @@
       </c>
       <c r="I237" s="9"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="6">
         <v>32721</v>
       </c>
@@ -5535,7 +5551,7 @@
       </c>
       <c r="I238" s="9"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="6">
         <v>32752</v>
       </c>
@@ -5556,7 +5572,7 @@
       </c>
       <c r="I239" s="9"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="6">
         <v>32782</v>
       </c>
@@ -5577,7 +5593,7 @@
       </c>
       <c r="I240" s="9"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="6">
         <v>32813</v>
       </c>
@@ -5598,7 +5614,7 @@
       </c>
       <c r="I241" s="9"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="6">
         <v>32843</v>
       </c>
@@ -5619,7 +5635,7 @@
       </c>
       <c r="I242" s="9"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" s="6">
         <v>32874</v>
       </c>
@@ -5640,7 +5656,7 @@
       </c>
       <c r="I243" s="9"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" s="6">
         <v>32905</v>
       </c>
@@ -5661,7 +5677,7 @@
       </c>
       <c r="I244" s="9"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" s="6">
         <v>32933</v>
       </c>
@@ -5682,7 +5698,7 @@
       </c>
       <c r="I245" s="9"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="6">
         <v>32964</v>
       </c>
@@ -5703,7 +5719,7 @@
       </c>
       <c r="I246" s="9"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="6">
         <v>32994</v>
       </c>
@@ -5724,7 +5740,7 @@
       </c>
       <c r="I247" s="9"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" s="6">
         <v>33025</v>
       </c>
@@ -5745,7 +5761,7 @@
       </c>
       <c r="I248" s="9"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" s="6">
         <v>33055</v>
       </c>
@@ -5766,7 +5782,7 @@
       </c>
       <c r="I249" s="9"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="6">
         <v>33086</v>
       </c>
@@ -5787,7 +5803,7 @@
       </c>
       <c r="I250" s="9"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" s="6">
         <v>33117</v>
       </c>
@@ -5808,7 +5824,7 @@
       </c>
       <c r="I251" s="9"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="6">
         <v>33147</v>
       </c>
@@ -5829,7 +5845,7 @@
       </c>
       <c r="I252" s="9"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" s="6">
         <v>33178</v>
       </c>
@@ -5850,7 +5866,7 @@
       </c>
       <c r="I253" s="9"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" s="6">
         <v>33208</v>
       </c>
@@ -5871,7 +5887,7 @@
       </c>
       <c r="I254" s="9"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" s="6">
         <v>33239</v>
       </c>
@@ -5892,7 +5908,7 @@
       </c>
       <c r="I255" s="9"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" s="6">
         <v>33270</v>
       </c>
@@ -5913,7 +5929,7 @@
       </c>
       <c r="I256" s="9"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" s="6">
         <v>33298</v>
       </c>
@@ -5934,7 +5950,7 @@
       </c>
       <c r="I257" s="9"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" s="6">
         <v>33329</v>
       </c>
@@ -5955,7 +5971,7 @@
       </c>
       <c r="I258" s="9"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" s="6">
         <v>33359</v>
       </c>
@@ -5976,7 +5992,7 @@
       </c>
       <c r="I259" s="9"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" s="6">
         <v>33390</v>
       </c>
@@ -5997,7 +6013,7 @@
       </c>
       <c r="I260" s="9"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" s="6">
         <v>33420</v>
       </c>
@@ -6018,7 +6034,7 @@
       </c>
       <c r="I261" s="9"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" s="6">
         <v>33451</v>
       </c>
@@ -6039,7 +6055,7 @@
       </c>
       <c r="I262" s="9"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" s="6">
         <v>33482</v>
       </c>
@@ -6060,7 +6076,7 @@
       </c>
       <c r="I263" s="9"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" s="6">
         <v>33512</v>
       </c>
@@ -6081,7 +6097,7 @@
       </c>
       <c r="I264" s="9"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" s="6">
         <v>33543</v>
       </c>
@@ -6102,7 +6118,7 @@
       </c>
       <c r="I265" s="9"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" s="6">
         <v>33573</v>
       </c>
@@ -6123,7 +6139,7 @@
       </c>
       <c r="I266" s="9"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" s="6">
         <v>33604</v>
       </c>
@@ -6144,7 +6160,7 @@
       </c>
       <c r="I267" s="9"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" s="6">
         <v>33635</v>
       </c>
@@ -6165,7 +6181,7 @@
       </c>
       <c r="I268" s="9"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" s="6">
         <v>33664</v>
       </c>
@@ -6186,7 +6202,7 @@
       </c>
       <c r="I269" s="9"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" s="6">
         <v>33695</v>
       </c>
@@ -6207,7 +6223,7 @@
       </c>
       <c r="I270" s="9"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" s="6">
         <v>33725</v>
       </c>
@@ -6228,7 +6244,7 @@
       </c>
       <c r="I271" s="9"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" s="6">
         <v>33756</v>
       </c>
@@ -6249,7 +6265,7 @@
       </c>
       <c r="I272" s="9"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" s="6">
         <v>33786</v>
       </c>
@@ -6270,7 +6286,7 @@
       </c>
       <c r="I273" s="9"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" s="6">
         <v>33817</v>
       </c>
@@ -6291,7 +6307,7 @@
       </c>
       <c r="I274" s="9"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" s="6">
         <v>33848</v>
       </c>
@@ -6312,7 +6328,7 @@
       </c>
       <c r="I275" s="9"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" s="6">
         <v>33878</v>
       </c>
@@ -6333,7 +6349,7 @@
       </c>
       <c r="I276" s="9"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="6">
         <v>33909</v>
       </c>
@@ -6354,7 +6370,7 @@
       </c>
       <c r="I277" s="9"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" s="6">
         <v>33939</v>
       </c>
@@ -6375,7 +6391,7 @@
       </c>
       <c r="I278" s="9"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" s="6">
         <v>33970</v>
       </c>
@@ -6396,7 +6412,7 @@
       </c>
       <c r="I279" s="9"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" s="6">
         <v>34001</v>
       </c>
@@ -6417,7 +6433,7 @@
       </c>
       <c r="I280" s="9"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" s="6">
         <v>34029</v>
       </c>
@@ -6438,7 +6454,7 @@
       </c>
       <c r="I281" s="9"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" s="6">
         <v>34060</v>
       </c>
@@ -6459,7 +6475,7 @@
       </c>
       <c r="I282" s="9"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" s="6">
         <v>34090</v>
       </c>
@@ -6480,7 +6496,7 @@
       </c>
       <c r="I283" s="9"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" s="6">
         <v>34121</v>
       </c>
@@ -6501,7 +6517,7 @@
       </c>
       <c r="I284" s="9"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" s="6">
         <v>34151</v>
       </c>
@@ -6522,7 +6538,7 @@
       </c>
       <c r="I285" s="9"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" s="6">
         <v>34182</v>
       </c>
@@ -6543,7 +6559,7 @@
       </c>
       <c r="I286" s="9"/>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" s="6">
         <v>34213</v>
       </c>
@@ -6564,7 +6580,7 @@
       </c>
       <c r="I287" s="9"/>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" s="6">
         <v>34243</v>
       </c>
@@ -6585,7 +6601,7 @@
       </c>
       <c r="I288" s="9"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" s="6">
         <v>34274</v>
       </c>
@@ -6606,7 +6622,7 @@
       </c>
       <c r="I289" s="9"/>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" s="6">
         <v>34304</v>
       </c>
@@ -6627,7 +6643,7 @@
       </c>
       <c r="I290" s="9"/>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" s="6">
         <v>34335</v>
       </c>
@@ -6648,7 +6664,7 @@
       </c>
       <c r="I291" s="9"/>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" s="6">
         <v>34366</v>
       </c>
@@ -6669,7 +6685,7 @@
       </c>
       <c r="I292" s="9"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" s="6">
         <v>34394</v>
       </c>
@@ -6690,7 +6706,7 @@
       </c>
       <c r="I293" s="9"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" s="6">
         <v>34425</v>
       </c>
@@ -6711,7 +6727,7 @@
       </c>
       <c r="I294" s="9"/>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" s="6">
         <v>34455</v>
       </c>
@@ -6732,7 +6748,7 @@
       </c>
       <c r="I295" s="9"/>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" s="6">
         <v>34486</v>
       </c>
@@ -6753,7 +6769,7 @@
       </c>
       <c r="I296" s="9"/>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" s="6">
         <v>34516</v>
       </c>
@@ -6774,7 +6790,7 @@
       </c>
       <c r="I297" s="9"/>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" s="6">
         <v>34547</v>
       </c>
@@ -6795,7 +6811,7 @@
       </c>
       <c r="I298" s="9"/>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" s="6">
         <v>34578</v>
       </c>
@@ -6816,7 +6832,7 @@
       </c>
       <c r="I299" s="9"/>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" s="6">
         <v>34608</v>
       </c>
@@ -6837,7 +6853,7 @@
       </c>
       <c r="I300" s="9"/>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" s="6">
         <v>34639</v>
       </c>
@@ -6858,7 +6874,7 @@
       </c>
       <c r="I301" s="9"/>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" s="6">
         <v>34669</v>
       </c>
@@ -6879,7 +6895,7 @@
       </c>
       <c r="I302" s="9"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" s="6">
         <v>34700</v>
       </c>
@@ -6900,7 +6916,7 @@
       </c>
       <c r="I303" s="9"/>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" s="6">
         <v>34731</v>
       </c>
@@ -6921,7 +6937,7 @@
       </c>
       <c r="I304" s="9"/>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" s="6">
         <v>34759</v>
       </c>
@@ -6942,7 +6958,7 @@
       </c>
       <c r="I305" s="9"/>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" s="6">
         <v>34790</v>
       </c>
@@ -6963,7 +6979,7 @@
       </c>
       <c r="I306" s="9"/>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" s="6">
         <v>34820</v>
       </c>
@@ -6984,7 +7000,7 @@
       </c>
       <c r="I307" s="9"/>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" s="6">
         <v>34851</v>
       </c>
@@ -7005,7 +7021,7 @@
       </c>
       <c r="I308" s="9"/>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" s="6">
         <v>34881</v>
       </c>
@@ -7026,7 +7042,7 @@
       </c>
       <c r="I309" s="9"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" s="6">
         <v>34912</v>
       </c>
@@ -7047,7 +7063,7 @@
       </c>
       <c r="I310" s="9"/>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" s="6">
         <v>34943</v>
       </c>
@@ -7068,7 +7084,7 @@
       </c>
       <c r="I311" s="9"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" s="6">
         <v>34973</v>
       </c>
@@ -7089,7 +7105,7 @@
       </c>
       <c r="I312" s="9"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" s="6">
         <v>35004</v>
       </c>
@@ -7110,7 +7126,7 @@
       </c>
       <c r="I313" s="9"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" s="6">
         <v>35034</v>
       </c>
@@ -7131,7 +7147,7 @@
       </c>
       <c r="I314" s="9"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" s="6">
         <v>35065</v>
       </c>
@@ -7152,7 +7168,7 @@
       </c>
       <c r="I315" s="9"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" s="6">
         <v>35096</v>
       </c>
@@ -7173,7 +7189,7 @@
       </c>
       <c r="I316" s="9"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" s="6">
         <v>35125</v>
       </c>
@@ -7194,7 +7210,7 @@
       </c>
       <c r="I317" s="9"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" s="6">
         <v>35156</v>
       </c>
@@ -7215,7 +7231,7 @@
       </c>
       <c r="I318" s="9"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" s="6">
         <v>35186</v>
       </c>
@@ -7236,7 +7252,7 @@
       </c>
       <c r="I319" s="9"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" s="6">
         <v>35217</v>
       </c>
@@ -7257,7 +7273,7 @@
       </c>
       <c r="I320" s="9"/>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" s="6">
         <v>35247</v>
       </c>
@@ -7278,7 +7294,7 @@
       </c>
       <c r="I321" s="9"/>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" s="6">
         <v>35278</v>
       </c>
@@ -7299,7 +7315,7 @@
       </c>
       <c r="I322" s="9"/>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" s="6">
         <v>35309</v>
       </c>
@@ -7320,7 +7336,7 @@
       </c>
       <c r="I323" s="9"/>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" s="6">
         <v>35339</v>
       </c>
@@ -7341,7 +7357,7 @@
       </c>
       <c r="I324" s="9"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" s="6">
         <v>35370</v>
       </c>
@@ -7362,7 +7378,7 @@
       </c>
       <c r="I325" s="9"/>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" s="6">
         <v>35400</v>
       </c>
@@ -7383,7 +7399,7 @@
       </c>
       <c r="I326" s="9"/>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" s="6">
         <v>35431</v>
       </c>
@@ -7404,7 +7420,7 @@
       </c>
       <c r="I327" s="9"/>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" s="6">
         <v>35462</v>
       </c>
@@ -7425,7 +7441,7 @@
       </c>
       <c r="I328" s="9"/>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" s="6">
         <v>35490</v>
       </c>
@@ -7446,7 +7462,7 @@
       </c>
       <c r="I329" s="9"/>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330" s="6">
         <v>35521</v>
       </c>
@@ -7467,7 +7483,7 @@
       </c>
       <c r="I330" s="9"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A331" s="6">
         <v>35551</v>
       </c>
@@ -7488,7 +7504,7 @@
       </c>
       <c r="I331" s="9"/>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A332" s="6">
         <v>35582</v>
       </c>
@@ -7509,7 +7525,7 @@
       </c>
       <c r="I332" s="9"/>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A333" s="6">
         <v>35612</v>
       </c>
@@ -7530,7 +7546,7 @@
       </c>
       <c r="I333" s="9"/>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A334" s="6">
         <v>35643</v>
       </c>
@@ -7551,7 +7567,7 @@
       </c>
       <c r="I334" s="9"/>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A335" s="6">
         <v>35674</v>
       </c>
@@ -7572,7 +7588,7 @@
       </c>
       <c r="I335" s="9"/>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A336" s="6">
         <v>35704</v>
       </c>
@@ -7593,7 +7609,7 @@
       </c>
       <c r="I336" s="9"/>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A337" s="6">
         <v>35735</v>
       </c>
@@ -7614,7 +7630,7 @@
       </c>
       <c r="I337" s="9"/>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A338" s="6">
         <v>35765</v>
       </c>
@@ -7635,7 +7651,7 @@
       </c>
       <c r="I338" s="9"/>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A339" s="6">
         <v>35796</v>
       </c>
@@ -7656,7 +7672,7 @@
       </c>
       <c r="I339" s="9"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340" s="6">
         <v>35827</v>
       </c>
@@ -7677,7 +7693,7 @@
       </c>
       <c r="I340" s="9"/>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341" s="6">
         <v>35855</v>
       </c>
@@ -7698,7 +7714,7 @@
       </c>
       <c r="I341" s="9"/>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342" s="6">
         <v>35886</v>
       </c>
@@ -7719,7 +7735,7 @@
       </c>
       <c r="I342" s="9"/>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343" s="6">
         <v>35916</v>
       </c>
@@ -7740,7 +7756,7 @@
       </c>
       <c r="I343" s="9"/>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A344" s="6">
         <v>35947</v>
       </c>
@@ -7761,7 +7777,7 @@
       </c>
       <c r="I344" s="9"/>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A345" s="6">
         <v>35977</v>
       </c>
@@ -7782,7 +7798,7 @@
       </c>
       <c r="I345" s="9"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A346" s="6">
         <v>36008</v>
       </c>
@@ -7803,7 +7819,7 @@
       </c>
       <c r="I346" s="9"/>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A347" s="6">
         <v>36039</v>
       </c>
@@ -7824,7 +7840,7 @@
       </c>
       <c r="I347" s="9"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A348" s="6">
         <v>36069</v>
       </c>
@@ -7845,7 +7861,7 @@
       </c>
       <c r="I348" s="9"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A349" s="6">
         <v>36100</v>
       </c>
@@ -7866,7 +7882,7 @@
       </c>
       <c r="I349" s="9"/>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A350" s="6">
         <v>36130</v>
       </c>
@@ -7887,7 +7903,7 @@
       </c>
       <c r="I350" s="9"/>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A351" s="6">
         <v>36161</v>
       </c>
@@ -7908,7 +7924,7 @@
       </c>
       <c r="I351" s="9"/>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352" s="6">
         <v>36192</v>
       </c>
@@ -7929,7 +7945,7 @@
       </c>
       <c r="I352" s="9"/>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353" s="6">
         <v>36220</v>
       </c>
@@ -7950,7 +7966,7 @@
       </c>
       <c r="I353" s="9"/>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A354" s="6">
         <v>36251</v>
       </c>
@@ -7971,7 +7987,7 @@
       </c>
       <c r="I354" s="9"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A355" s="6">
         <v>36281</v>
       </c>
@@ -7992,7 +8008,7 @@
       </c>
       <c r="I355" s="9"/>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A356" s="6">
         <v>36312</v>
       </c>
@@ -8013,7 +8029,7 @@
       </c>
       <c r="I356" s="9"/>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A357" s="6">
         <v>36342</v>
       </c>
@@ -8034,7 +8050,7 @@
       </c>
       <c r="I357" s="9"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A358" s="6">
         <v>36373</v>
       </c>
@@ -8055,7 +8071,7 @@
       </c>
       <c r="I358" s="9"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A359" s="6">
         <v>36404</v>
       </c>
@@ -8076,7 +8092,7 @@
       </c>
       <c r="I359" s="9"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A360" s="6">
         <v>36434</v>
       </c>
@@ -8097,7 +8113,7 @@
       </c>
       <c r="I360" s="9"/>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A361" s="6">
         <v>36465</v>
       </c>
@@ -8118,7 +8134,7 @@
       </c>
       <c r="I361" s="9"/>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A362" s="6">
         <v>36495</v>
       </c>
@@ -8139,7 +8155,7 @@
       </c>
       <c r="I362" s="9"/>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A363" s="6">
         <v>36526</v>
       </c>
@@ -8160,7 +8176,7 @@
       </c>
       <c r="I363" s="9"/>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A364" s="6">
         <v>36557</v>
       </c>
@@ -8181,7 +8197,7 @@
       </c>
       <c r="I364" s="9"/>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A365" s="6">
         <v>36586</v>
       </c>
@@ -8202,7 +8218,7 @@
       </c>
       <c r="I365" s="9"/>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A366" s="6">
         <v>36617</v>
       </c>
@@ -8223,7 +8239,7 @@
       </c>
       <c r="I366" s="9"/>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A367" s="6">
         <v>36647</v>
       </c>
@@ -8244,7 +8260,7 @@
       </c>
       <c r="I367" s="9"/>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A368" s="6">
         <v>36678</v>
       </c>
@@ -8265,7 +8281,7 @@
       </c>
       <c r="I368" s="9"/>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A369" s="6">
         <v>36708</v>
       </c>
@@ -8286,7 +8302,7 @@
       </c>
       <c r="I369" s="9"/>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A370" s="6">
         <v>36739</v>
       </c>
@@ -8307,7 +8323,7 @@
       </c>
       <c r="I370" s="9"/>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A371" s="6">
         <v>36770</v>
       </c>
@@ -8328,7 +8344,7 @@
       </c>
       <c r="I371" s="9"/>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A372" s="6">
         <v>36800</v>
       </c>
@@ -8349,7 +8365,7 @@
       </c>
       <c r="I372" s="9"/>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A373" s="6">
         <v>36831</v>
       </c>
@@ -8370,7 +8386,7 @@
       </c>
       <c r="I373" s="9"/>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A374" s="6">
         <v>36861</v>
       </c>
@@ -8391,7 +8407,7 @@
       </c>
       <c r="I374" s="9"/>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A375" s="6">
         <v>36892</v>
       </c>
@@ -8412,7 +8428,7 @@
       </c>
       <c r="I375" s="9"/>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A376" s="6">
         <v>36923</v>
       </c>
@@ -8433,7 +8449,7 @@
       </c>
       <c r="I376" s="9"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A377" s="6">
         <v>36951</v>
       </c>
@@ -8454,7 +8470,7 @@
       </c>
       <c r="I377" s="9"/>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A378" s="6">
         <v>36982</v>
       </c>
@@ -8475,7 +8491,7 @@
       </c>
       <c r="I378" s="9"/>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A379" s="6">
         <v>37012</v>
       </c>
@@ -8496,7 +8512,7 @@
       </c>
       <c r="I379" s="9"/>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A380" s="6">
         <v>37043</v>
       </c>
@@ -8517,7 +8533,7 @@
       </c>
       <c r="I380" s="9"/>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A381" s="6">
         <v>37073</v>
       </c>
@@ -8538,7 +8554,7 @@
       </c>
       <c r="I381" s="9"/>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A382" s="6">
         <v>37104</v>
       </c>
@@ -8559,7 +8575,7 @@
       </c>
       <c r="I382" s="9"/>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A383" s="6">
         <v>37135</v>
       </c>
@@ -8580,7 +8596,7 @@
       </c>
       <c r="I383" s="9"/>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A384" s="6">
         <v>37165</v>
       </c>
@@ -8601,7 +8617,7 @@
       </c>
       <c r="I384" s="9"/>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A385" s="6">
         <v>37196</v>
       </c>
@@ -8622,7 +8638,7 @@
       </c>
       <c r="I385" s="9"/>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A386" s="6">
         <v>37226</v>
       </c>
@@ -8643,7 +8659,7 @@
       </c>
       <c r="I386" s="9"/>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A387" s="6">
         <v>37257</v>
       </c>
@@ -8664,7 +8680,7 @@
       </c>
       <c r="I387" s="9"/>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A388" s="6">
         <v>37288</v>
       </c>
@@ -8685,7 +8701,7 @@
       </c>
       <c r="I388" s="9"/>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A389" s="6">
         <v>37316</v>
       </c>
@@ -8706,7 +8722,7 @@
       </c>
       <c r="I389" s="9"/>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A390" s="6">
         <v>37347</v>
       </c>
@@ -8727,7 +8743,7 @@
       </c>
       <c r="I390" s="9"/>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A391" s="6">
         <v>37377</v>
       </c>
@@ -8748,7 +8764,7 @@
       </c>
       <c r="I391" s="9"/>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A392" s="6">
         <v>37408</v>
       </c>
@@ -8769,7 +8785,7 @@
       </c>
       <c r="I392" s="9"/>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A393" s="6">
         <v>37438</v>
       </c>
@@ -8790,7 +8806,7 @@
       </c>
       <c r="I393" s="9"/>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A394" s="6">
         <v>37469</v>
       </c>
@@ -8811,7 +8827,7 @@
       </c>
       <c r="I394" s="9"/>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A395" s="6">
         <v>37500</v>
       </c>
@@ -8832,7 +8848,7 @@
       </c>
       <c r="I395" s="9"/>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A396" s="6">
         <v>37530</v>
       </c>
@@ -8853,7 +8869,7 @@
       </c>
       <c r="I396" s="9"/>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A397" s="6">
         <v>37561</v>
       </c>
@@ -8874,7 +8890,7 @@
       </c>
       <c r="I397" s="9"/>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A398" s="6">
         <v>37591</v>
       </c>
@@ -8895,7 +8911,7 @@
       </c>
       <c r="I398" s="9"/>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A399" s="6">
         <v>37622</v>
       </c>
@@ -8916,7 +8932,7 @@
       </c>
       <c r="I399" s="9"/>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A400" s="6">
         <v>37653</v>
       </c>
@@ -8937,7 +8953,7 @@
       </c>
       <c r="I400" s="9"/>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A401" s="6">
         <v>37681</v>
       </c>
@@ -8958,7 +8974,7 @@
       </c>
       <c r="I401" s="9"/>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A402" s="6">
         <v>37712</v>
       </c>
@@ -8979,7 +8995,7 @@
       </c>
       <c r="I402" s="9"/>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A403" s="6">
         <v>37742</v>
       </c>
@@ -9000,7 +9016,7 @@
       </c>
       <c r="I403" s="9"/>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A404" s="6">
         <v>37773</v>
       </c>
@@ -9021,7 +9037,7 @@
       </c>
       <c r="I404" s="9"/>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A405" s="6">
         <v>37803</v>
       </c>
@@ -9042,7 +9058,7 @@
       </c>
       <c r="I405" s="9"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A406" s="6">
         <v>37834</v>
       </c>
@@ -9063,7 +9079,7 @@
       </c>
       <c r="I406" s="9"/>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A407" s="6">
         <v>37865</v>
       </c>
@@ -9084,7 +9100,7 @@
       </c>
       <c r="I407" s="9"/>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A408" s="6">
         <v>37895</v>
       </c>
@@ -9105,7 +9121,7 @@
       </c>
       <c r="I408" s="9"/>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A409" s="6">
         <v>37926</v>
       </c>
@@ -9126,7 +9142,7 @@
       </c>
       <c r="I409" s="9"/>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A410" s="6">
         <v>37956</v>
       </c>
@@ -9147,7 +9163,7 @@
       </c>
       <c r="I410" s="9"/>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A411" s="6">
         <v>37987</v>
       </c>
@@ -9168,7 +9184,7 @@
       </c>
       <c r="I411" s="9"/>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A412" s="6">
         <v>38018</v>
       </c>
@@ -9189,7 +9205,7 @@
       </c>
       <c r="I412" s="9"/>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A413" s="6">
         <v>38047</v>
       </c>
@@ -9210,7 +9226,7 @@
       </c>
       <c r="I413" s="9"/>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A414" s="6">
         <v>38078</v>
       </c>
@@ -9231,7 +9247,7 @@
       </c>
       <c r="I414" s="9"/>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A415" s="6">
         <v>38108</v>
       </c>
@@ -9252,7 +9268,7 @@
       </c>
       <c r="I415" s="9"/>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A416" s="6">
         <v>38139</v>
       </c>
@@ -9273,7 +9289,7 @@
       </c>
       <c r="I416" s="9"/>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A417" s="6">
         <v>38169</v>
       </c>
@@ -9294,7 +9310,7 @@
       </c>
       <c r="I417" s="9"/>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A418" s="6">
         <v>38200</v>
       </c>
@@ -9315,7 +9331,7 @@
       </c>
       <c r="I418" s="9"/>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A419" s="6">
         <v>38231</v>
       </c>
@@ -9336,7 +9352,7 @@
       </c>
       <c r="I419" s="9"/>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A420" s="6">
         <v>38261</v>
       </c>
@@ -9357,7 +9373,7 @@
       </c>
       <c r="I420" s="9"/>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A421" s="6">
         <v>38292</v>
       </c>
@@ -9378,7 +9394,7 @@
       </c>
       <c r="I421" s="9"/>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A422" s="6">
         <v>38322</v>
       </c>
@@ -9399,7 +9415,7 @@
       </c>
       <c r="I422" s="9"/>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A423" s="6">
         <v>38353</v>
       </c>
@@ -9420,7 +9436,7 @@
       </c>
       <c r="I423" s="9"/>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A424" s="6">
         <v>38384</v>
       </c>
@@ -9441,7 +9457,7 @@
       </c>
       <c r="I424" s="9"/>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A425" s="6">
         <v>38412</v>
       </c>
@@ -9462,7 +9478,7 @@
       </c>
       <c r="I425" s="9"/>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A426" s="6">
         <v>38443</v>
       </c>
@@ -9483,7 +9499,7 @@
       </c>
       <c r="I426" s="9"/>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A427" s="6">
         <v>38473</v>
       </c>
@@ -9504,7 +9520,7 @@
       </c>
       <c r="I427" s="9"/>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A428" s="6">
         <v>38504</v>
       </c>
@@ -9525,7 +9541,7 @@
       </c>
       <c r="I428" s="9"/>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A429" s="6">
         <v>38534</v>
       </c>
@@ -9546,7 +9562,7 @@
       </c>
       <c r="I429" s="9"/>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A430" s="6">
         <v>38565</v>
       </c>
@@ -9567,7 +9583,7 @@
       </c>
       <c r="I430" s="9"/>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A431" s="6">
         <v>38596</v>
       </c>
@@ -9588,7 +9604,7 @@
       </c>
       <c r="I431" s="9"/>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A432" s="6">
         <v>38626</v>
       </c>
@@ -9609,7 +9625,7 @@
       </c>
       <c r="I432" s="9"/>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A433" s="6">
         <v>38657</v>
       </c>
@@ -9630,7 +9646,7 @@
       </c>
       <c r="I433" s="9"/>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A434" s="6">
         <v>38687</v>
       </c>
@@ -9651,7 +9667,7 @@
       </c>
       <c r="I434" s="9"/>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A435" s="6">
         <v>38718</v>
       </c>
@@ -9672,7 +9688,7 @@
       </c>
       <c r="I435" s="9"/>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A436" s="6">
         <v>38749</v>
       </c>
@@ -9693,7 +9709,7 @@
       </c>
       <c r="I436" s="9"/>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A437" s="6">
         <v>38777</v>
       </c>
@@ -9714,7 +9730,7 @@
       </c>
       <c r="I437" s="9"/>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A438" s="6">
         <v>38808</v>
       </c>
@@ -9735,7 +9751,7 @@
       </c>
       <c r="I438" s="9"/>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A439" s="6">
         <v>38838</v>
       </c>
@@ -9756,7 +9772,7 @@
       </c>
       <c r="I439" s="9"/>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A440" s="6">
         <v>38869</v>
       </c>
@@ -9777,7 +9793,7 @@
       </c>
       <c r="I440" s="9"/>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A441" s="6">
         <v>38899</v>
       </c>
@@ -9798,7 +9814,7 @@
       </c>
       <c r="I441" s="9"/>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A442" s="6">
         <v>38930</v>
       </c>
@@ -9819,7 +9835,7 @@
       </c>
       <c r="I442" s="9"/>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A443" s="6">
         <v>38961</v>
       </c>
@@ -9840,7 +9856,7 @@
       </c>
       <c r="I443" s="9"/>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A444" s="6">
         <v>38991</v>
       </c>
@@ -9861,7 +9877,7 @@
       </c>
       <c r="I444" s="9"/>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A445" s="6">
         <v>39022</v>
       </c>
@@ -9882,7 +9898,7 @@
       </c>
       <c r="I445" s="9"/>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A446" s="6">
         <v>39052</v>
       </c>
@@ -9903,7 +9919,7 @@
       </c>
       <c r="I446" s="9"/>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A447" s="6">
         <v>39083</v>
       </c>
@@ -9924,7 +9940,7 @@
       </c>
       <c r="I447" s="9"/>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A448" s="6">
         <v>39114</v>
       </c>
@@ -9945,7 +9961,7 @@
       </c>
       <c r="I448" s="9"/>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A449" s="6">
         <v>39142</v>
       </c>
@@ -9966,7 +9982,7 @@
       </c>
       <c r="I449" s="9"/>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A450" s="6">
         <v>39173</v>
       </c>
@@ -9987,7 +10003,7 @@
       </c>
       <c r="I450" s="9"/>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A451" s="6">
         <v>39203</v>
       </c>
@@ -10008,7 +10024,7 @@
       </c>
       <c r="I451" s="9"/>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A452" s="6">
         <v>39234</v>
       </c>
@@ -10029,7 +10045,7 @@
       </c>
       <c r="I452" s="9"/>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A453" s="6">
         <v>39264</v>
       </c>
@@ -10050,7 +10066,7 @@
       </c>
       <c r="I453" s="9"/>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A454" s="6">
         <v>39295</v>
       </c>
@@ -10071,7 +10087,7 @@
       </c>
       <c r="I454" s="9"/>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A455" s="6">
         <v>39326</v>
       </c>
@@ -10092,7 +10108,7 @@
       </c>
       <c r="I455" s="9"/>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A456" s="6">
         <v>39356</v>
       </c>
@@ -10113,7 +10129,7 @@
       </c>
       <c r="I456" s="9"/>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A457" s="6">
         <v>39387</v>
       </c>
@@ -10134,7 +10150,7 @@
       </c>
       <c r="I457" s="9"/>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A458" s="6">
         <v>39417</v>
       </c>
@@ -10155,7 +10171,7 @@
       </c>
       <c r="I458" s="9"/>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A459" s="6">
         <v>39448</v>
       </c>
@@ -10176,7 +10192,7 @@
       </c>
       <c r="I459" s="9"/>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A460" s="6">
         <v>39479</v>
       </c>
@@ -10197,7 +10213,7 @@
       </c>
       <c r="I460" s="9"/>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A461" s="6">
         <v>39508</v>
       </c>
@@ -10218,7 +10234,7 @@
       </c>
       <c r="I461" s="9"/>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A462" s="6">
         <v>39539</v>
       </c>
@@ -10239,7 +10255,7 @@
       </c>
       <c r="I462" s="9"/>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A463" s="6">
         <v>39569</v>
       </c>
@@ -10260,7 +10276,7 @@
       </c>
       <c r="I463" s="9"/>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A464" s="6">
         <v>39600</v>
       </c>
@@ -10281,7 +10297,7 @@
       </c>
       <c r="I464" s="9"/>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A465" s="6">
         <v>39630</v>
       </c>
@@ -10302,7 +10318,7 @@
       </c>
       <c r="I465" s="9"/>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A466" s="6">
         <v>39661</v>
       </c>
@@ -10323,7 +10339,7 @@
       </c>
       <c r="I466" s="9"/>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A467" s="6">
         <v>39692</v>
       </c>
@@ -10344,7 +10360,7 @@
       </c>
       <c r="I467" s="9"/>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A468" s="6">
         <v>39722</v>
       </c>
@@ -10365,7 +10381,7 @@
       </c>
       <c r="I468" s="9"/>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A469" s="6">
         <v>39753</v>
       </c>
@@ -10386,7 +10402,7 @@
       </c>
       <c r="I469" s="9"/>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A470" s="6">
         <v>39783</v>
       </c>
@@ -10407,7 +10423,7 @@
       </c>
       <c r="I470" s="9"/>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A471" s="6">
         <v>39814</v>
       </c>
@@ -10428,7 +10444,7 @@
       </c>
       <c r="I471" s="9"/>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A472" s="6">
         <v>39845</v>
       </c>
@@ -10449,7 +10465,7 @@
       </c>
       <c r="I472" s="9"/>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A473" s="6">
         <v>39873</v>
       </c>
@@ -10470,7 +10486,7 @@
       </c>
       <c r="I473" s="9"/>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A474" s="6">
         <v>39904</v>
       </c>
@@ -10491,7 +10507,7 @@
       </c>
       <c r="I474" s="9"/>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A475" s="6">
         <v>39934</v>
       </c>
@@ -10512,7 +10528,7 @@
       </c>
       <c r="I475" s="9"/>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A476" s="6">
         <v>39965</v>
       </c>
@@ -10533,7 +10549,7 @@
       </c>
       <c r="I476" s="9"/>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A477" s="6">
         <v>39995</v>
       </c>
@@ -10554,7 +10570,7 @@
       </c>
       <c r="I477" s="9"/>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A478" s="6">
         <v>40026</v>
       </c>
@@ -10575,7 +10591,7 @@
       </c>
       <c r="I478" s="9"/>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A479" s="6">
         <v>40057</v>
       </c>
@@ -10596,7 +10612,7 @@
       </c>
       <c r="I479" s="9"/>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A480" s="6">
         <v>40087</v>
       </c>
@@ -10617,7 +10633,7 @@
       </c>
       <c r="I480" s="9"/>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A481" s="6">
         <v>40118</v>
       </c>
@@ -10638,7 +10654,7 @@
       </c>
       <c r="I481" s="9"/>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A482" s="6">
         <v>40148</v>
       </c>
@@ -10659,7 +10675,7 @@
       </c>
       <c r="I482" s="9"/>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A483" s="6">
         <v>40179</v>
       </c>
@@ -10680,7 +10696,7 @@
       </c>
       <c r="I483" s="9"/>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A484" s="6">
         <v>40210</v>
       </c>
@@ -10701,7 +10717,7 @@
       </c>
       <c r="I484" s="9"/>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A485" s="6">
         <v>40238</v>
       </c>
@@ -10722,7 +10738,7 @@
       </c>
       <c r="I485" s="9"/>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A486" s="6">
         <v>40269</v>
       </c>
@@ -10743,7 +10759,7 @@
       </c>
       <c r="I486" s="9"/>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A487" s="6">
         <v>40299</v>
       </c>
@@ -10764,7 +10780,7 @@
       </c>
       <c r="I487" s="9"/>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A488" s="6">
         <v>40330</v>
       </c>
@@ -10785,7 +10801,7 @@
       </c>
       <c r="I488" s="9"/>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A489" s="6">
         <v>40360</v>
       </c>
@@ -10806,7 +10822,7 @@
       </c>
       <c r="I489" s="9"/>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A490" s="6">
         <v>40391</v>
       </c>
@@ -10827,7 +10843,7 @@
       </c>
       <c r="I490" s="9"/>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A491" s="6">
         <v>40422</v>
       </c>
@@ -10848,7 +10864,7 @@
       </c>
       <c r="I491" s="9"/>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A492" s="6">
         <v>40452</v>
       </c>
@@ -10869,7 +10885,7 @@
       </c>
       <c r="I492" s="9"/>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A493" s="6">
         <v>40483</v>
       </c>
@@ -10890,7 +10906,7 @@
       </c>
       <c r="I493" s="9"/>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A494" s="6">
         <v>40513</v>
       </c>
@@ -10911,7 +10927,7 @@
       </c>
       <c r="I494" s="9"/>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A495" s="6">
         <v>40544</v>
       </c>
@@ -10932,7 +10948,7 @@
       </c>
       <c r="I495" s="9"/>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A496" s="6">
         <v>40575</v>
       </c>
@@ -10953,7 +10969,7 @@
       </c>
       <c r="I496" s="9"/>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A497" s="6">
         <v>40603</v>
       </c>
@@ -10974,7 +10990,7 @@
       </c>
       <c r="I497" s="9"/>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A498" s="6">
         <v>40634</v>
       </c>
@@ -10995,7 +11011,7 @@
       </c>
       <c r="I498" s="9"/>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A499" s="6">
         <v>40664</v>
       </c>
@@ -11016,7 +11032,7 @@
       </c>
       <c r="I499" s="9"/>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A500" s="6">
         <v>40695</v>
       </c>
@@ -11037,7 +11053,7 @@
       </c>
       <c r="I500" s="9"/>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A501" s="6">
         <v>40725</v>
       </c>
@@ -11058,7 +11074,7 @@
       </c>
       <c r="I501" s="9"/>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A502" s="6">
         <v>40756</v>
       </c>
@@ -11079,7 +11095,7 @@
       </c>
       <c r="I502" s="9"/>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A503" s="6">
         <v>40787</v>
       </c>
@@ -11100,7 +11116,7 @@
       </c>
       <c r="I503" s="9"/>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A504" s="6">
         <v>40817</v>
       </c>
@@ -11121,7 +11137,7 @@
       </c>
       <c r="I504" s="9"/>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A505" s="6">
         <v>40848</v>
       </c>
@@ -11142,7 +11158,7 @@
       </c>
       <c r="I505" s="9"/>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A506" s="6">
         <v>40878</v>
       </c>
@@ -11163,7 +11179,7 @@
       </c>
       <c r="I506" s="9"/>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A507" s="6">
         <v>40909</v>
       </c>
@@ -11184,7 +11200,7 @@
       </c>
       <c r="I507" s="9"/>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A508" s="6">
         <v>40940</v>
       </c>
@@ -11205,7 +11221,7 @@
       </c>
       <c r="I508" s="9"/>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A509" s="6">
         <v>40969</v>
       </c>
@@ -11226,7 +11242,7 @@
       </c>
       <c r="I509" s="9"/>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A510" s="6">
         <v>41000</v>
       </c>
@@ -11247,7 +11263,7 @@
       </c>
       <c r="I510" s="9"/>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A511" s="6">
         <v>41030</v>
       </c>
@@ -11268,7 +11284,7 @@
       </c>
       <c r="I511" s="9"/>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A512" s="6">
         <v>41061</v>
       </c>
@@ -11289,7 +11305,7 @@
       </c>
       <c r="I512" s="9"/>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A513" s="6">
         <v>41091</v>
       </c>
@@ -11310,7 +11326,7 @@
       </c>
       <c r="I513" s="9"/>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A514" s="6">
         <v>41122</v>
       </c>
@@ -11331,7 +11347,7 @@
       </c>
       <c r="I514" s="9"/>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A515" s="6">
         <v>41153</v>
       </c>
@@ -11352,7 +11368,7 @@
       </c>
       <c r="I515" s="9"/>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A516" s="6">
         <v>41183</v>
       </c>
@@ -11373,7 +11389,7 @@
       </c>
       <c r="I516" s="9"/>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A517" s="6">
         <v>41214</v>
       </c>
@@ -11394,7 +11410,7 @@
       </c>
       <c r="I517" s="9"/>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A518" s="6">
         <v>41244</v>
       </c>
@@ -11415,7 +11431,7 @@
       </c>
       <c r="I518" s="9"/>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A519" s="6">
         <v>41275</v>
       </c>
@@ -11436,7 +11452,7 @@
       </c>
       <c r="I519" s="9"/>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A520" s="6">
         <v>41306</v>
       </c>
@@ -11457,7 +11473,7 @@
       </c>
       <c r="I520" s="9"/>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A521" s="6">
         <v>41334</v>
       </c>
@@ -11478,7 +11494,7 @@
       </c>
       <c r="I521" s="9"/>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A522" s="6">
         <v>41365</v>
       </c>
@@ -11499,7 +11515,7 @@
       </c>
       <c r="I522" s="9"/>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A523" s="6">
         <v>41395</v>
       </c>
@@ -11520,7 +11536,7 @@
       </c>
       <c r="I523" s="9"/>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A524" s="6">
         <v>41426</v>
       </c>
@@ -11541,7 +11557,7 @@
       </c>
       <c r="I524" s="9"/>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A525" s="6">
         <v>41456</v>
       </c>
@@ -11562,7 +11578,7 @@
       </c>
       <c r="I525" s="9"/>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A526" s="6">
         <v>41487</v>
       </c>
@@ -11583,7 +11599,7 @@
       </c>
       <c r="I526" s="9"/>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A527" s="6">
         <v>41518</v>
       </c>
@@ -11604,7 +11620,7 @@
       </c>
       <c r="I527" s="9"/>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A528" s="6">
         <v>41548</v>
       </c>
@@ -11625,7 +11641,7 @@
       </c>
       <c r="I528" s="9"/>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A529" s="6">
         <v>41579</v>
       </c>
@@ -11646,7 +11662,7 @@
       </c>
       <c r="I529" s="9"/>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A530" s="6">
         <v>41609</v>
       </c>
@@ -11667,7 +11683,7 @@
       </c>
       <c r="I530" s="9"/>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A531" s="6">
         <v>41640</v>
       </c>
@@ -11688,7 +11704,7 @@
       </c>
       <c r="I531" s="9"/>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A532" s="6">
         <v>41671</v>
       </c>
@@ -11709,7 +11725,7 @@
       </c>
       <c r="I532" s="9"/>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A533" s="6">
         <v>41699</v>
       </c>
@@ -11730,7 +11746,7 @@
       </c>
       <c r="I533" s="9"/>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A534" s="6">
         <v>41730</v>
       </c>
@@ -11751,7 +11767,7 @@
       </c>
       <c r="I534" s="9"/>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A535" s="6">
         <v>41760</v>
       </c>
@@ -11772,7 +11788,7 @@
       </c>
       <c r="I535" s="9"/>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A536" s="6">
         <v>41791</v>
       </c>
@@ -11793,7 +11809,7 @@
       </c>
       <c r="I536" s="9"/>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A537" s="6">
         <v>41821</v>
       </c>
@@ -11814,7 +11830,7 @@
       </c>
       <c r="I537" s="9"/>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A538" s="6">
         <v>41852</v>
       </c>
@@ -11841,7 +11857,7 @@
       </c>
       <c r="I538" s="9"/>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A539" s="6">
         <v>41852</v>
       </c>
@@ -11862,7 +11878,7 @@
       </c>
       <c r="I539" s="9"/>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A540" s="6">
         <v>41883</v>
       </c>
@@ -11889,7 +11905,7 @@
       </c>
       <c r="I540" s="9"/>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A541" s="6">
         <v>41913</v>
       </c>
@@ -11916,7 +11932,7 @@
       </c>
       <c r="I541" s="9"/>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A542" s="6">
         <v>41913</v>
       </c>
@@ -11937,7 +11953,7 @@
       </c>
       <c r="I542" s="9"/>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A543" s="6">
         <v>41944</v>
       </c>
@@ -11964,7 +11980,7 @@
       </c>
       <c r="I543" s="9"/>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A544" s="6">
         <v>41944</v>
       </c>
@@ -11985,7 +12001,7 @@
       </c>
       <c r="I544" s="9"/>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A545" s="6">
         <v>41974</v>
       </c>
@@ -12012,7 +12028,7 @@
       </c>
       <c r="I545" s="9"/>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A546" s="6">
         <v>41974</v>
       </c>
@@ -12033,7 +12049,7 @@
       </c>
       <c r="I546" s="9"/>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A547" s="6">
         <v>42005</v>
       </c>
@@ -12060,7 +12076,7 @@
       </c>
       <c r="I547" s="9"/>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A548" s="6">
         <v>42005</v>
       </c>
@@ -12081,7 +12097,7 @@
       </c>
       <c r="I548" s="9"/>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A549" s="6">
         <v>42036</v>
       </c>
@@ -12108,7 +12124,7 @@
       </c>
       <c r="I549" s="9"/>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A550" s="6">
         <v>42036</v>
       </c>
@@ -12129,7 +12145,7 @@
       </c>
       <c r="I550" s="9"/>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A551" s="6">
         <v>42064</v>
       </c>
@@ -12156,7 +12172,7 @@
       </c>
       <c r="I551" s="9"/>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A552" s="6">
         <v>42064</v>
       </c>
@@ -12177,7 +12193,7 @@
       </c>
       <c r="I552" s="9"/>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A553" s="6">
         <v>42095</v>
       </c>
@@ -12204,7 +12220,7 @@
       </c>
       <c r="I553" s="9"/>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A554" s="6">
         <v>42095</v>
       </c>
@@ -12228,7 +12244,7 @@
       </c>
       <c r="I554" s="9"/>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A555" s="6">
         <v>42125</v>
       </c>
@@ -12255,7 +12271,7 @@
       </c>
       <c r="I555" s="9"/>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A556" s="6">
         <v>42125</v>
       </c>
@@ -12276,7 +12292,7 @@
       </c>
       <c r="I556" s="9"/>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A557" s="6">
         <v>42156</v>
       </c>
@@ -12303,7 +12319,7 @@
       </c>
       <c r="I557" s="9"/>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A558" s="6">
         <v>42156</v>
       </c>
@@ -12327,7 +12343,7 @@
       </c>
       <c r="I558" s="9"/>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A559" s="6">
         <v>42186</v>
       </c>
@@ -12354,7 +12370,7 @@
       </c>
       <c r="I559" s="9"/>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A560" s="6">
         <v>42186</v>
       </c>
@@ -12375,7 +12391,7 @@
       </c>
       <c r="I560" s="9"/>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A561" s="6">
         <v>42217</v>
       </c>
@@ -12402,7 +12418,7 @@
       </c>
       <c r="I561" s="9"/>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A562" s="6">
         <v>42217</v>
       </c>
@@ -12423,7 +12439,7 @@
       </c>
       <c r="I562" s="9"/>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A563" s="6">
         <v>42248</v>
       </c>
@@ -12450,7 +12466,7 @@
       </c>
       <c r="I563" s="9"/>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A564" s="6">
         <v>42248</v>
       </c>
@@ -12471,7 +12487,7 @@
       </c>
       <c r="I564" s="9"/>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A565" s="6">
         <v>42278</v>
       </c>
@@ -12498,7 +12514,7 @@
       </c>
       <c r="I565" s="9"/>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A566" s="6">
         <v>42278</v>
       </c>
@@ -12522,7 +12538,7 @@
       </c>
       <c r="I566" s="9"/>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A567" s="6">
         <v>42309</v>
       </c>
@@ -12549,7 +12565,7 @@
       </c>
       <c r="I567" s="9"/>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A568" s="6">
         <v>42309</v>
       </c>
@@ -12570,7 +12586,7 @@
       </c>
       <c r="I568" s="9"/>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A569" s="6">
         <v>42339</v>
       </c>
@@ -12597,7 +12613,7 @@
       </c>
       <c r="I569" s="9"/>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A570" s="6">
         <v>42339</v>
       </c>
@@ -12618,7 +12634,7 @@
       </c>
       <c r="I570" s="9"/>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A571" s="6">
         <v>42370</v>
       </c>
@@ -12645,7 +12661,7 @@
       </c>
       <c r="I571" s="9"/>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A572" s="6">
         <v>42370</v>
       </c>
@@ -12669,7 +12685,7 @@
       </c>
       <c r="I572" s="9"/>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A573" s="6">
         <v>42401</v>
       </c>
@@ -12696,7 +12712,7 @@
       </c>
       <c r="I573" s="9"/>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A574" s="6">
         <v>42430</v>
       </c>
@@ -12723,7 +12739,7 @@
       </c>
       <c r="I574" s="9"/>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A575" s="6">
         <v>42430</v>
       </c>
@@ -12747,7 +12763,7 @@
       </c>
       <c r="I575" s="9"/>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A576" s="6">
         <v>42461</v>
       </c>
@@ -12774,7 +12790,7 @@
       </c>
       <c r="I576" s="9"/>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A577" s="6">
         <v>42461</v>
       </c>
@@ -12798,7 +12814,7 @@
       </c>
       <c r="I577" s="9"/>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A578" s="6">
         <v>42491</v>
       </c>
@@ -12825,7 +12841,7 @@
       </c>
       <c r="I578" s="9"/>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A579" s="6">
         <v>42491</v>
       </c>
@@ -12849,7 +12865,7 @@
       </c>
       <c r="I579" s="9"/>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A580" s="6">
         <v>42522</v>
       </c>
@@ -12873,7 +12889,7 @@
       </c>
       <c r="I580" s="9"/>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A581" s="6">
         <v>42522</v>
       </c>
@@ -12897,7 +12913,7 @@
       </c>
       <c r="I581" s="9"/>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A582" s="6">
         <v>42552</v>
       </c>
@@ -12924,7 +12940,7 @@
       </c>
       <c r="I582" s="9"/>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A583" s="6">
         <v>42552</v>
       </c>
@@ -12948,7 +12964,7 @@
       </c>
       <c r="I583" s="9"/>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A584" s="6">
         <v>42583</v>
       </c>
@@ -12975,7 +12991,7 @@
       </c>
       <c r="I584" s="9"/>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A585" s="6">
         <v>42614</v>
       </c>
@@ -13002,7 +13018,7 @@
       </c>
       <c r="I585" s="9"/>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A586" s="6">
         <v>42644</v>
       </c>
@@ -13029,7 +13045,7 @@
       </c>
       <c r="I586" s="9"/>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A587" s="6">
         <v>42644</v>
       </c>
@@ -13050,7 +13066,7 @@
       </c>
       <c r="I587" s="9"/>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A588" s="6">
         <v>42675</v>
       </c>
@@ -13077,7 +13093,7 @@
       </c>
       <c r="I588" s="9"/>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A589" s="6">
         <v>42675</v>
       </c>
@@ -13098,7 +13114,7 @@
       </c>
       <c r="I589" s="9"/>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A590" s="6">
         <v>42705</v>
       </c>
@@ -13125,7 +13141,7 @@
       </c>
       <c r="I590" s="9"/>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A591" s="6">
         <v>42705</v>
       </c>
@@ -13149,7 +13165,7 @@
       </c>
       <c r="I591" s="9"/>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A592" s="6">
         <v>42736</v>
       </c>
@@ -13176,7 +13192,7 @@
       </c>
       <c r="I592" s="9"/>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A593" s="6">
         <v>42767</v>
       </c>
@@ -13203,7 +13219,7 @@
       </c>
       <c r="I593" s="9"/>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A594" s="6">
         <v>42795</v>
       </c>
@@ -13230,7 +13246,7 @@
       </c>
       <c r="I594" s="9"/>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A595" s="6">
         <v>42826</v>
       </c>
@@ -13257,7 +13273,7 @@
       </c>
       <c r="I595" s="9"/>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A596" s="6">
         <v>42856</v>
       </c>
@@ -13284,7 +13300,7 @@
       </c>
       <c r="I596" s="9"/>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A597" s="6">
         <v>42887</v>
       </c>
@@ -13311,7 +13327,7 @@
       </c>
       <c r="I597" s="9"/>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A598" s="6">
         <v>42887</v>
       </c>
@@ -13332,7 +13348,7 @@
       </c>
       <c r="I598" s="9"/>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A599" s="6">
         <v>42917</v>
       </c>
@@ -13356,7 +13372,7 @@
       </c>
       <c r="I599" s="9"/>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A600" s="6">
         <v>42917</v>
       </c>
@@ -13380,7 +13396,7 @@
       </c>
       <c r="I600" s="9"/>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A601" s="6">
         <v>42948</v>
       </c>
@@ -13404,7 +13420,7 @@
       </c>
       <c r="I601" s="9"/>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A602" s="6">
         <v>42948</v>
       </c>
@@ -13428,7 +13444,7 @@
       </c>
       <c r="I602" s="9"/>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A603" s="6">
         <v>42979</v>
       </c>
@@ -13452,7 +13468,7 @@
       </c>
       <c r="I603" s="9"/>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A604" s="6">
         <v>42979</v>
       </c>
@@ -13476,7 +13492,7 @@
       </c>
       <c r="I604" s="9"/>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A605" s="6">
         <v>43009</v>
       </c>
@@ -13503,7 +13519,7 @@
       </c>
       <c r="I605" s="9"/>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A606" s="6">
         <v>43009</v>
       </c>
@@ -13527,7 +13543,7 @@
       </c>
       <c r="I606" s="9"/>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A607" s="6">
         <v>43040</v>
       </c>
@@ -13554,7 +13570,7 @@
       </c>
       <c r="I607" s="9"/>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A608" s="6">
         <v>43040</v>
       </c>
@@ -13578,7 +13594,7 @@
       </c>
       <c r="I608" s="9"/>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A609" s="6">
         <v>43070</v>
       </c>
@@ -13605,7 +13621,7 @@
       </c>
       <c r="I609" s="9"/>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A610" s="6">
         <v>43070</v>
       </c>
@@ -13626,7 +13642,7 @@
       </c>
       <c r="I610" s="9"/>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A611" s="6">
         <v>43101</v>
       </c>
@@ -13653,7 +13669,7 @@
       </c>
       <c r="I611" s="9"/>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A612" s="6">
         <v>43101</v>
       </c>
@@ -13674,7 +13690,7 @@
       </c>
       <c r="I612" s="9"/>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A613" s="6">
         <v>43132</v>
       </c>
@@ -13701,7 +13717,7 @@
       </c>
       <c r="I613" s="9"/>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A614" s="6">
         <v>43132</v>
       </c>
@@ -13722,7 +13738,7 @@
       </c>
       <c r="I614" s="9"/>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A615" s="6">
         <v>43160</v>
       </c>
@@ -13749,7 +13765,7 @@
       </c>
       <c r="I615" s="9"/>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A616" s="6">
         <v>43160</v>
       </c>
@@ -13770,7 +13786,7 @@
       </c>
       <c r="I616" s="9"/>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A617" s="6">
         <v>43191</v>
       </c>
@@ -13797,7 +13813,7 @@
       </c>
       <c r="I617" s="9"/>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A618" s="6">
         <v>43221</v>
       </c>
@@ -13824,7 +13840,7 @@
       </c>
       <c r="I618" s="9"/>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A619" s="6">
         <v>43221</v>
       </c>
@@ -13845,7 +13861,7 @@
       </c>
       <c r="I619" s="9"/>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A620" s="6">
         <v>43252</v>
       </c>
@@ -13872,7 +13888,7 @@
       </c>
       <c r="I620" s="9"/>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A621" s="6">
         <v>43252</v>
       </c>
@@ -13893,7 +13909,7 @@
       </c>
       <c r="I621" s="9"/>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A622" s="6">
         <v>43282</v>
       </c>
@@ -13920,7 +13936,7 @@
       </c>
       <c r="I622" s="9"/>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A623" s="6">
         <v>43282</v>
       </c>
@@ -13941,7 +13957,7 @@
       </c>
       <c r="I623" s="9"/>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A624" s="6">
         <v>43313</v>
       </c>
@@ -13968,7 +13984,7 @@
       </c>
       <c r="I624" s="9"/>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A625" s="6">
         <v>43313</v>
       </c>
@@ -13989,7 +14005,7 @@
       </c>
       <c r="I625" s="9"/>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A626" s="6">
         <v>43344</v>
       </c>
@@ -14016,7 +14032,7 @@
       </c>
       <c r="I626" s="9"/>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A627" s="6">
         <v>43344</v>
       </c>
@@ -14037,7 +14053,7 @@
       </c>
       <c r="I627" s="9"/>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A628" s="6">
         <v>43374</v>
       </c>
@@ -14064,7 +14080,7 @@
       </c>
       <c r="I628" s="9"/>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A629" s="6">
         <v>43374</v>
       </c>
@@ -14085,7 +14101,7 @@
       </c>
       <c r="I629" s="9"/>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A630" s="6">
         <v>43405</v>
       </c>
@@ -14112,7 +14128,7 @@
       </c>
       <c r="I630" s="9"/>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A631" s="6">
         <v>43405</v>
       </c>
@@ -14133,7 +14149,7 @@
       </c>
       <c r="I631" s="9"/>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A632" s="6">
         <v>43435</v>
       </c>
@@ -14160,7 +14176,7 @@
       </c>
       <c r="I632" s="9"/>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A633" s="6">
         <v>43466</v>
       </c>
@@ -14187,7 +14203,7 @@
       </c>
       <c r="I633" s="9"/>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A634" s="6">
         <v>43466</v>
       </c>
@@ -14208,7 +14224,7 @@
       </c>
       <c r="I634" s="9"/>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A635" s="6">
         <v>43497</v>
       </c>
@@ -14235,7 +14251,7 @@
       </c>
       <c r="I635" s="9"/>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A636" s="6">
         <v>43497</v>
       </c>
@@ -14256,7 +14272,7 @@
       </c>
       <c r="I636" s="9"/>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A637" s="6">
         <v>43525</v>
       </c>
@@ -14283,7 +14299,7 @@
       </c>
       <c r="I637" s="9"/>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A638" s="6">
         <v>43525</v>
       </c>
@@ -14304,7 +14320,7 @@
       </c>
       <c r="I638" s="9"/>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A639" s="6">
         <v>43556</v>
       </c>
@@ -14331,7 +14347,7 @@
       </c>
       <c r="I639" s="9"/>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A640" s="6">
         <v>43586</v>
       </c>
@@ -14358,7 +14374,7 @@
       </c>
       <c r="I640" s="9"/>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A641" s="6">
         <v>43617</v>
       </c>
@@ -14385,7 +14401,7 @@
       </c>
       <c r="I641" s="9"/>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A642" s="6">
         <v>43647</v>
       </c>
@@ -14412,7 +14428,7 @@
       </c>
       <c r="I642" s="9"/>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A643" s="6">
         <v>43678</v>
       </c>
@@ -14439,7 +14455,7 @@
       </c>
       <c r="I643" s="9"/>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A644" s="6">
         <v>43678</v>
       </c>
@@ -14460,7 +14476,7 @@
       </c>
       <c r="I644" s="9"/>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A645" s="6">
         <v>43709</v>
       </c>
@@ -14487,7 +14503,7 @@
       </c>
       <c r="I645" s="9"/>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A646" s="6">
         <v>43709</v>
       </c>
@@ -14508,7 +14524,7 @@
       </c>
       <c r="I646" s="9"/>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A647" s="6">
         <v>43739</v>
       </c>
@@ -14535,7 +14551,7 @@
       </c>
       <c r="I647" s="9"/>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A648" s="6">
         <v>43739</v>
       </c>
@@ -14556,7 +14572,7 @@
       </c>
       <c r="I648" s="9"/>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A649" s="6">
         <v>43770</v>
       </c>
@@ -14583,7 +14599,7 @@
       </c>
       <c r="I649" s="9"/>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A650" s="6">
         <v>43800</v>
       </c>
@@ -14610,7 +14626,7 @@
       </c>
       <c r="I650" s="9"/>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A651" s="6">
         <v>43831</v>
       </c>
@@ -14637,7 +14653,7 @@
       </c>
       <c r="I651" s="9"/>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A652" s="6">
         <v>43862</v>
       </c>
@@ -14664,7 +14680,7 @@
       </c>
       <c r="I652" s="9"/>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A653" s="6">
         <v>43891</v>
       </c>
@@ -14691,7 +14707,7 @@
       </c>
       <c r="I653" s="9"/>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A654" s="6">
         <v>43891</v>
       </c>
@@ -14712,7 +14728,7 @@
       </c>
       <c r="I654" s="9"/>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A655" s="6">
         <v>43922</v>
       </c>
@@ -14739,7 +14755,7 @@
       </c>
       <c r="I655" s="9"/>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A656" s="6">
         <v>43922</v>
       </c>
@@ -14760,7 +14776,7 @@
       </c>
       <c r="I656" s="9"/>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A657" s="6">
         <v>43952</v>
       </c>
@@ -14787,7 +14803,7 @@
       </c>
       <c r="I657" s="9"/>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A658" s="6">
         <v>43952</v>
       </c>
@@ -14808,7 +14824,7 @@
       </c>
       <c r="I658" s="9"/>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A659" s="6">
         <v>43983</v>
       </c>
@@ -14835,7 +14851,7 @@
       </c>
       <c r="I659" s="9"/>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A660" s="6">
         <v>43983</v>
       </c>
@@ -14856,7 +14872,7 @@
       </c>
       <c r="I660" s="9"/>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A661" s="6">
         <v>44013</v>
       </c>
@@ -14883,7 +14899,7 @@
       </c>
       <c r="I661" s="9"/>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A662" s="6">
         <v>44044</v>
       </c>
@@ -14910,7 +14926,7 @@
       </c>
       <c r="I662" s="9"/>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A663" s="6">
         <v>44044</v>
       </c>
@@ -14931,7 +14947,7 @@
       </c>
       <c r="I663" s="9"/>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A664" s="6">
         <v>44075</v>
       </c>
@@ -14958,7 +14974,7 @@
       </c>
       <c r="I664" s="9"/>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A665" s="6">
         <v>44075</v>
       </c>
@@ -14979,7 +14995,7 @@
       </c>
       <c r="I665" s="9"/>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A666" s="6">
         <v>44105</v>
       </c>
@@ -15006,7 +15022,7 @@
       </c>
       <c r="I666" s="9"/>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A667" s="6">
         <v>44105</v>
       </c>
@@ -15027,7 +15043,7 @@
       </c>
       <c r="I667" s="9"/>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A668" s="6">
         <v>44136</v>
       </c>
@@ -15054,7 +15070,7 @@
       </c>
       <c r="I668" s="9"/>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A669" s="6">
         <v>44136</v>
       </c>
@@ -15075,7 +15091,7 @@
       </c>
       <c r="I669" s="9"/>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A670" s="6">
         <v>44166</v>
       </c>
@@ -15102,7 +15118,7 @@
       </c>
       <c r="I670" s="9"/>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A671" s="6">
         <v>44166</v>
       </c>
@@ -15123,7 +15139,7 @@
       </c>
       <c r="I671" s="9"/>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A672" s="6">
         <v>44197</v>
       </c>
@@ -15150,7 +15166,7 @@
       </c>
       <c r="I672" s="9"/>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A673" s="6">
         <v>44197</v>
       </c>
@@ -15171,7 +15187,7 @@
       </c>
       <c r="I673" s="9"/>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A674" s="6">
         <v>44228</v>
       </c>
@@ -15198,7 +15214,7 @@
       </c>
       <c r="I674" s="9"/>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A675" s="6">
         <v>44228</v>
       </c>
@@ -15219,7 +15235,7 @@
       </c>
       <c r="I675" s="9"/>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A676" s="6">
         <v>44256</v>
       </c>
@@ -15246,7 +15262,7 @@
       </c>
       <c r="I676" s="9"/>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A677" s="6">
         <v>44256</v>
       </c>
@@ -15267,7 +15283,7 @@
       </c>
       <c r="I677" s="9"/>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A678" s="6">
         <v>44287</v>
       </c>
@@ -15294,7 +15310,7 @@
       </c>
       <c r="I678" s="9"/>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A679" s="6">
         <v>44287</v>
       </c>
@@ -15315,7 +15331,7 @@
       </c>
       <c r="I679" s="9"/>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A680" s="6">
         <v>44317</v>
       </c>
@@ -15342,7 +15358,7 @@
       </c>
       <c r="I680" s="9"/>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A681" s="6">
         <v>44317</v>
       </c>
@@ -15363,7 +15379,7 @@
       </c>
       <c r="I681" s="9"/>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A682" s="6">
         <v>44348</v>
       </c>
@@ -15390,7 +15406,7 @@
       </c>
       <c r="I682" s="9"/>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A683" s="6">
         <v>44348</v>
       </c>
@@ -15411,7 +15427,7 @@
       </c>
       <c r="I683" s="9"/>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A684" s="6">
         <v>44378</v>
       </c>
@@ -15438,7 +15454,7 @@
       </c>
       <c r="I684" s="9"/>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A685" s="6">
         <v>44378</v>
       </c>
@@ -15459,7 +15475,7 @@
       </c>
       <c r="I685" s="9"/>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A686" s="6">
         <v>44409</v>
       </c>
@@ -15486,7 +15502,7 @@
       </c>
       <c r="I686" s="9"/>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A687" s="6">
         <v>44409</v>
       </c>
@@ -15507,7 +15523,7 @@
       </c>
       <c r="I687" s="9"/>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A688" s="6">
         <v>44440</v>
       </c>
@@ -15534,7 +15550,7 @@
       </c>
       <c r="I688" s="9"/>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A689" s="6">
         <v>44440</v>
       </c>
@@ -15555,7 +15571,7 @@
       </c>
       <c r="I689" s="9"/>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A690" s="6">
         <v>44470</v>
       </c>
@@ -15582,7 +15598,7 @@
       </c>
       <c r="I690" s="9"/>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A691" s="6">
         <v>44470</v>
       </c>
@@ -15603,7 +15619,7 @@
       </c>
       <c r="I691" s="9"/>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A692" s="6">
         <v>44501</v>
       </c>
@@ -15630,7 +15646,7 @@
       </c>
       <c r="I692" s="9"/>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A693" s="6">
         <v>44501</v>
       </c>
@@ -15651,7 +15667,7 @@
       </c>
       <c r="I693" s="9"/>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A694" s="6">
         <v>44531</v>
       </c>
@@ -15678,7 +15694,7 @@
       </c>
       <c r="I694" s="9"/>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A695" s="6">
         <v>44562</v>
       </c>
@@ -15705,7 +15721,7 @@
       </c>
       <c r="I695" s="9"/>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A696" s="6">
         <v>44562</v>
       </c>
@@ -15726,7 +15742,7 @@
       </c>
       <c r="I696" s="9"/>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A697" s="6">
         <v>44593</v>
       </c>
@@ -15753,7 +15769,7 @@
       </c>
       <c r="I697" s="9"/>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A698" s="6">
         <v>44593</v>
       </c>
@@ -15774,7 +15790,7 @@
       </c>
       <c r="I698" s="9"/>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A699" s="6">
         <v>44621</v>
       </c>
@@ -15801,7 +15817,7 @@
       </c>
       <c r="I699" s="9"/>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A700" s="6">
         <v>44621</v>
       </c>
@@ -15822,7 +15838,7 @@
       </c>
       <c r="I700" s="9"/>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A701" s="6">
         <v>44652</v>
       </c>
@@ -15849,7 +15865,7 @@
       </c>
       <c r="I701" s="9"/>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A702" s="6">
         <v>44652</v>
       </c>
@@ -15870,7 +15886,7 @@
       </c>
       <c r="I702" s="9"/>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A703" s="6">
         <v>44682</v>
       </c>
@@ -15897,7 +15913,7 @@
       </c>
       <c r="I703" s="9"/>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A704" s="6">
         <v>44682</v>
       </c>
@@ -15918,7 +15934,7 @@
       </c>
       <c r="I704" s="9"/>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A705" s="6">
         <v>44713</v>
       </c>
@@ -15945,7 +15961,7 @@
       </c>
       <c r="I705" s="9"/>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A706" s="6">
         <v>44713</v>
       </c>
@@ -15966,7 +15982,7 @@
       </c>
       <c r="I706" s="9"/>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A707" s="6">
         <v>44743</v>
       </c>
@@ -15993,7 +16009,7 @@
       </c>
       <c r="I707" s="9"/>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A708" s="6">
         <v>44743</v>
       </c>
@@ -16014,7 +16030,7 @@
       </c>
       <c r="I708" s="9"/>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A709" s="6">
         <v>44774</v>
       </c>
@@ -16041,7 +16057,7 @@
       </c>
       <c r="I709" s="9"/>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A710" s="6">
         <v>44774</v>
       </c>
@@ -16062,7 +16078,7 @@
       </c>
       <c r="I710" s="9"/>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A711" s="6">
         <v>44805</v>
       </c>
@@ -16089,7 +16105,7 @@
       </c>
       <c r="I711" s="9"/>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A712" s="6">
         <v>44835</v>
       </c>
@@ -16110,7 +16126,7 @@
       </c>
       <c r="I712" s="9"/>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A713" s="6">
         <v>44805</v>
       </c>
@@ -16131,7 +16147,7 @@
       </c>
       <c r="I713" s="9"/>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A714" s="6">
         <v>44835</v>
       </c>
@@ -16158,7 +16174,7 @@
       </c>
       <c r="I714" s="9"/>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A715" s="6">
         <v>44835</v>
       </c>
@@ -16179,7 +16195,7 @@
       </c>
       <c r="I715" s="9"/>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A716" s="6">
         <v>44866</v>
       </c>
@@ -16206,7 +16222,7 @@
       </c>
       <c r="I716" s="9"/>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A717" s="6">
         <v>44866</v>
       </c>
@@ -16227,7 +16243,7 @@
       </c>
       <c r="I717" s="9"/>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A718" s="6">
         <v>44896</v>
       </c>
@@ -16254,7 +16270,7 @@
       </c>
       <c r="I718" s="9"/>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A719" s="6">
         <v>44896</v>
       </c>
@@ -16275,7 +16291,7 @@
       </c>
       <c r="I719" s="9"/>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A720" s="6">
         <v>44927</v>
       </c>
@@ -16302,7 +16318,7 @@
       </c>
       <c r="I720" s="9"/>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A721" s="6">
         <v>44927</v>
       </c>
@@ -16323,7 +16339,7 @@
       </c>
       <c r="I721" s="9"/>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A722" s="6">
         <v>44958</v>
       </c>
@@ -16350,7 +16366,7 @@
       </c>
       <c r="I722" s="9"/>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A723" s="6">
         <v>44958</v>
       </c>
@@ -16374,7 +16390,7 @@
       </c>
       <c r="I723" s="9"/>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A724" s="6">
         <v>44986</v>
       </c>
@@ -16401,7 +16417,7 @@
       </c>
       <c r="I724" s="9"/>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A725" s="6">
         <v>44986</v>
       </c>
@@ -16425,7 +16441,7 @@
       </c>
       <c r="I725" s="9"/>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A726" s="6">
         <v>45017</v>
       </c>
@@ -16452,7 +16468,7 @@
       </c>
       <c r="I726" s="9"/>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A727" s="6">
         <v>45017</v>
       </c>
@@ -16476,7 +16492,7 @@
       </c>
       <c r="I727" s="9"/>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A728" s="6">
         <v>45047</v>
       </c>
@@ -16503,7 +16519,7 @@
       </c>
       <c r="I728" s="9"/>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A729" s="6">
         <v>45047</v>
       </c>
@@ -16527,7 +16543,7 @@
       </c>
       <c r="I729" s="9"/>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A730" s="6">
         <v>45078</v>
       </c>
@@ -16554,7 +16570,7 @@
       </c>
       <c r="I730" s="9"/>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A731" s="6">
         <v>45078</v>
       </c>
@@ -16578,7 +16594,7 @@
       </c>
       <c r="I731" s="9"/>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A732" s="6">
         <v>45108</v>
       </c>
@@ -16605,7 +16621,7 @@
       </c>
       <c r="I732" s="9"/>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A733" s="6">
         <v>45108</v>
       </c>
@@ -16626,7 +16642,7 @@
       </c>
       <c r="I733" s="9"/>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A734" s="6">
         <v>45139</v>
       </c>
@@ -16653,7 +16669,7 @@
       </c>
       <c r="I734" s="9"/>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A735" s="6">
         <v>45139</v>
       </c>
@@ -16677,7 +16693,7 @@
       </c>
       <c r="I735" s="9"/>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A736" s="6">
         <v>45170</v>
       </c>
@@ -16704,7 +16720,7 @@
       </c>
       <c r="I736" s="9"/>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A737" s="6">
         <v>45200</v>
       </c>
@@ -16731,7 +16747,7 @@
       </c>
       <c r="I737" s="9"/>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A738" s="6">
         <v>45231</v>
       </c>
@@ -16758,7 +16774,7 @@
       </c>
       <c r="I738" s="9"/>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A739" s="6">
         <v>45261</v>
       </c>
@@ -16785,7 +16801,7 @@
       </c>
       <c r="I739" s="9"/>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A740" s="6">
         <v>45261</v>
       </c>
@@ -16806,7 +16822,7 @@
       </c>
       <c r="I740" s="9"/>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A741" s="6">
         <v>45292</v>
       </c>
@@ -16833,7 +16849,7 @@
       </c>
       <c r="I741" s="9"/>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A742" s="6">
         <v>45323</v>
       </c>
@@ -16860,7 +16876,7 @@
       </c>
       <c r="I742" s="9"/>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A743" s="6">
         <v>45352</v>
       </c>
@@ -16887,7 +16903,7 @@
       </c>
       <c r="I743" s="9"/>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A744" s="6">
         <v>45352</v>
       </c>
@@ -16908,7 +16924,7 @@
       </c>
       <c r="I744" s="9"/>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A745" s="6">
         <v>45383</v>
       </c>
@@ -16935,7 +16951,7 @@
       </c>
       <c r="I745" s="9"/>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A746" s="6">
         <v>45413</v>
       </c>
@@ -16959,7 +16975,7 @@
       </c>
       <c r="I746" s="9"/>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A747" s="6">
         <v>45444</v>
       </c>
@@ -16986,7 +17002,7 @@
       </c>
       <c r="I747" s="9"/>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A748" s="6">
         <v>45444</v>
       </c>
@@ -17007,7 +17023,7 @@
       </c>
       <c r="I748" s="9"/>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A749" s="6">
         <v>45474</v>
       </c>
@@ -17034,7 +17050,7 @@
       </c>
       <c r="I749" s="9"/>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A750" s="6">
         <v>45474</v>
       </c>
@@ -17055,7 +17071,7 @@
       </c>
       <c r="I750" s="9"/>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A751" s="6">
         <v>45505</v>
       </c>
@@ -17082,7 +17098,7 @@
       </c>
       <c r="I751" s="9"/>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A752" s="6">
         <v>45505</v>
       </c>
@@ -17103,7 +17119,7 @@
       </c>
       <c r="I752" s="9"/>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A753" s="6">
         <v>45536</v>
       </c>
@@ -17127,7 +17143,7 @@
       </c>
       <c r="I753" s="9"/>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A754" s="6">
         <v>45566</v>
       </c>
@@ -17154,7 +17170,7 @@
       </c>
       <c r="I754" s="9"/>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A755" s="6">
         <v>45566</v>
       </c>
@@ -17175,7 +17191,7 @@
       </c>
       <c r="I755" s="9"/>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A756" s="6">
         <v>45597</v>
       </c>
@@ -17196,7 +17212,7 @@
       </c>
       <c r="I756" s="9"/>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A757" s="6">
         <v>45597</v>
       </c>
@@ -17217,7 +17233,7 @@
       </c>
       <c r="I757" s="9"/>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A758" s="6">
         <v>45627</v>
       </c>
@@ -17244,7 +17260,7 @@
       </c>
       <c r="I758" s="9"/>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A759" s="6">
         <v>45627</v>
       </c>
@@ -17268,7 +17284,7 @@
       </c>
       <c r="I759" s="9"/>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A760" s="6">
         <v>45658</v>
       </c>
@@ -17295,7 +17311,7 @@
       </c>
       <c r="I760" s="9"/>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A761" s="6">
         <v>45658</v>
       </c>
@@ -17319,7 +17335,7 @@
       </c>
       <c r="I761" s="9"/>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A762" s="6">
         <v>45689</v>
       </c>
@@ -17346,7 +17362,7 @@
       </c>
       <c r="I762" s="9"/>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A763" s="6">
         <v>45689</v>
       </c>
@@ -17370,7 +17386,7 @@
       </c>
       <c r="I763" s="9"/>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A764" s="6">
         <v>45717</v>
       </c>
@@ -17397,7 +17413,7 @@
       </c>
       <c r="I764" s="9"/>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A765" s="6">
         <v>45717</v>
       </c>
@@ -17421,7 +17437,7 @@
       </c>
       <c r="I765" s="9"/>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A766" s="6">
         <v>45748</v>
       </c>
@@ -17448,7 +17464,7 @@
       </c>
       <c r="I766" s="9"/>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A767" s="6">
         <v>45748</v>
       </c>
@@ -17472,7 +17488,7 @@
       </c>
       <c r="I767" s="9"/>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A768" s="6">
         <v>45778</v>
       </c>
@@ -17499,7 +17515,7 @@
       </c>
       <c r="I768" s="9"/>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A769" s="6">
         <v>45778</v>
       </c>
@@ -17523,7 +17539,7 @@
       </c>
       <c r="I769" s="9"/>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A770" s="6">
         <v>45809</v>
       </c>
@@ -17550,7 +17566,7 @@
       </c>
       <c r="I770" s="9"/>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A771" s="6">
         <v>45809</v>
       </c>
@@ -17574,7 +17590,7 @@
       </c>
       <c r="I771" s="9"/>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A772" s="6">
         <v>45839</v>
       </c>
@@ -17601,7 +17617,7 @@
       </c>
       <c r="I772" s="9"/>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A773" s="6">
         <v>45870</v>
       </c>
@@ -17628,7 +17644,7 @@
       </c>
       <c r="I773" s="9"/>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A774" s="6">
         <v>45870</v>
       </c>
@@ -17652,7 +17668,7 @@
       </c>
       <c r="I774" s="9"/>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A775" s="6">
         <v>45901</v>
       </c>
@@ -17679,7 +17695,7 @@
       </c>
       <c r="I775" s="9"/>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A776" s="6">
         <v>45901</v>
       </c>
@@ -17703,7 +17719,7 @@
       </c>
       <c r="I776" s="9"/>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A777" s="6">
         <v>45931</v>
       </c>
@@ -17727,7 +17743,7 @@
       </c>
       <c r="I777" s="9"/>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A778" s="6">
         <v>45931</v>
       </c>
@@ -17748,7 +17764,7 @@
       </c>
       <c r="I778" s="9"/>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A779" s="6">
         <v>45962</v>
       </c>
@@ -17775,7 +17791,7 @@
       </c>
       <c r="I779" s="9"/>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A780" s="6">
         <v>45962</v>
       </c>
@@ -17799,7 +17815,7 @@
       </c>
       <c r="I780" s="9"/>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A781" s="6">
         <v>45992</v>
       </c>
@@ -17825,7 +17841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A782" s="6">
         <v>45992</v>
       </c>
@@ -17848,7 +17864,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A783" s="6">
         <v>46023</v>
       </c>
@@ -17874,7 +17890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A784" s="6">
         <v>46023</v>
       </c>
@@ -17897,7 +17913,7 @@
         <v>0.13300000000000001</v>
       </c>
     </row>
-    <row r="785" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A785" s="6">
         <v>46054</v>
       </c>
@@ -17923,7 +17939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="786" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A786" s="6">
         <v>46054</v>
       </c>
@@ -17936,9 +17952,58 @@
       <c r="D786" s="7" t="s">
         <v>6</v>
       </c>
+      <c r="E786" s="12">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="F786" s="12">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G786" s="12">
+        <v>0.33800000000000002</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A787" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B787" s="6">
+        <v>46113</v>
+      </c>
+      <c r="C787" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="D787" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E787" s="12">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="F787" s="12">
+        <v>0.44900000000000001</v>
+      </c>
+      <c r="G787" s="12">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="H787" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A788" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B788" s="6">
+        <v>46127</v>
+      </c>
+      <c r="C788" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="D788" s="7" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="B2:G781">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G781">
     <sortCondition ref="B2:B781"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -17950,32 +18015,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF29D08C-57DE-47BE-A1D1-3528FC9A6DD6}">
   <dimension ref="B1:C3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{0CF4A770-3A48-4748-BD91-9A05092BAAF2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>